--- a/data/nzd0257/nzd0257.xlsx
+++ b/data/nzd0257/nzd0257.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD316"/>
+  <dimension ref="A1:AD319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30606,7 +30606,7 @@
         <v>350.78</v>
       </c>
       <c r="P315" t="n">
-        <v>357.76</v>
+        <v>362.78</v>
       </c>
       <c r="Q315" t="n">
         <v>362.53</v>
@@ -30702,7 +30702,7 @@
         <v>334.8</v>
       </c>
       <c r="P316" t="n">
-        <v>346.32</v>
+        <v>354.7</v>
       </c>
       <c r="Q316" t="n">
         <v>351.83</v>
@@ -30746,6 +30746,294 @@
       <c r="AD316" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:49+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>359.1</v>
+      </c>
+      <c r="C317" t="n">
+        <v>338.15</v>
+      </c>
+      <c r="D317" t="n">
+        <v>337.36</v>
+      </c>
+      <c r="E317" t="n">
+        <v>333.02</v>
+      </c>
+      <c r="F317" t="n">
+        <v>328.3</v>
+      </c>
+      <c r="G317" t="n">
+        <v>324.37</v>
+      </c>
+      <c r="H317" t="n">
+        <v>323.52</v>
+      </c>
+      <c r="I317" t="n">
+        <v>327.45</v>
+      </c>
+      <c r="J317" t="n">
+        <v>335.35</v>
+      </c>
+      <c r="K317" t="n">
+        <v>345.32</v>
+      </c>
+      <c r="L317" t="n">
+        <v>349.18</v>
+      </c>
+      <c r="M317" t="n">
+        <v>353.38</v>
+      </c>
+      <c r="N317" t="n">
+        <v>346.79</v>
+      </c>
+      <c r="O317" t="n">
+        <v>323.44</v>
+      </c>
+      <c r="P317" t="n">
+        <v>353.94</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>349.3</v>
+      </c>
+      <c r="R317" t="n">
+        <v>353.24</v>
+      </c>
+      <c r="S317" t="n">
+        <v>351.44</v>
+      </c>
+      <c r="T317" t="n">
+        <v>360.04</v>
+      </c>
+      <c r="U317" t="n">
+        <v>363.72</v>
+      </c>
+      <c r="V317" t="n">
+        <v>364.13</v>
+      </c>
+      <c r="W317" t="n">
+        <v>355.95</v>
+      </c>
+      <c r="X317" t="n">
+        <v>358.85</v>
+      </c>
+      <c r="Y317" t="n">
+        <v>358.11</v>
+      </c>
+      <c r="Z317" t="n">
+        <v>357.6</v>
+      </c>
+      <c r="AA317" t="n">
+        <v>349.41</v>
+      </c>
+      <c r="AB317" t="n">
+        <v>349.51</v>
+      </c>
+      <c r="AC317" t="n">
+        <v>340.6</v>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>359.1</v>
+      </c>
+      <c r="C318" t="n">
+        <v>338.15</v>
+      </c>
+      <c r="D318" t="n">
+        <v>337.36</v>
+      </c>
+      <c r="E318" t="n">
+        <v>333.02</v>
+      </c>
+      <c r="F318" t="n">
+        <v>328.3</v>
+      </c>
+      <c r="G318" t="n">
+        <v>324.37</v>
+      </c>
+      <c r="H318" t="n">
+        <v>323.52</v>
+      </c>
+      <c r="I318" t="n">
+        <v>327.45</v>
+      </c>
+      <c r="J318" t="n">
+        <v>335.35</v>
+      </c>
+      <c r="K318" t="n">
+        <v>348.05</v>
+      </c>
+      <c r="L318" t="n">
+        <v>350.61</v>
+      </c>
+      <c r="M318" t="n">
+        <v>353.38</v>
+      </c>
+      <c r="N318" t="n">
+        <v>346.79</v>
+      </c>
+      <c r="O318" t="n">
+        <v>323.44</v>
+      </c>
+      <c r="P318" t="n">
+        <v>402.55</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="R318" t="n">
+        <v>352.5</v>
+      </c>
+      <c r="S318" t="n">
+        <v>351</v>
+      </c>
+      <c r="T318" t="n">
+        <v>358.52</v>
+      </c>
+      <c r="U318" t="n">
+        <v>362.67</v>
+      </c>
+      <c r="V318" t="n">
+        <v>361.9</v>
+      </c>
+      <c r="W318" t="n">
+        <v>356.14</v>
+      </c>
+      <c r="X318" t="n">
+        <v>356.98</v>
+      </c>
+      <c r="Y318" t="n">
+        <v>353.97</v>
+      </c>
+      <c r="Z318" t="n">
+        <v>352.52</v>
+      </c>
+      <c r="AA318" t="n">
+        <v>346.51</v>
+      </c>
+      <c r="AB318" t="n">
+        <v>348.56</v>
+      </c>
+      <c r="AC318" t="n">
+        <v>345.57</v>
+      </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>358.17</v>
+      </c>
+      <c r="C319" t="n">
+        <v>337.08</v>
+      </c>
+      <c r="D319" t="n">
+        <v>336.69</v>
+      </c>
+      <c r="E319" t="n">
+        <v>332.88</v>
+      </c>
+      <c r="F319" t="n">
+        <v>328.28</v>
+      </c>
+      <c r="G319" t="n">
+        <v>323.95</v>
+      </c>
+      <c r="H319" t="n">
+        <v>323.25</v>
+      </c>
+      <c r="I319" t="n">
+        <v>327.93</v>
+      </c>
+      <c r="J319" t="n">
+        <v>335.92</v>
+      </c>
+      <c r="K319" t="n">
+        <v>347.37</v>
+      </c>
+      <c r="L319" t="n">
+        <v>351.15</v>
+      </c>
+      <c r="M319" t="n">
+        <v>353.38</v>
+      </c>
+      <c r="N319" t="n">
+        <v>346.79</v>
+      </c>
+      <c r="O319" t="n">
+        <v>323.44</v>
+      </c>
+      <c r="P319" t="n">
+        <v>402.55</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="R319" t="n">
+        <v>352.5</v>
+      </c>
+      <c r="S319" t="n">
+        <v>351</v>
+      </c>
+      <c r="T319" t="n">
+        <v>358.52</v>
+      </c>
+      <c r="U319" t="n">
+        <v>362.67</v>
+      </c>
+      <c r="V319" t="n">
+        <v>361.6</v>
+      </c>
+      <c r="W319" t="n">
+        <v>355.61</v>
+      </c>
+      <c r="X319" t="n">
+        <v>356.1</v>
+      </c>
+      <c r="Y319" t="n">
+        <v>353.04</v>
+      </c>
+      <c r="Z319" t="n">
+        <v>351.89</v>
+      </c>
+      <c r="AA319" t="n">
+        <v>347.84</v>
+      </c>
+      <c r="AB319" t="n">
+        <v>350.26</v>
+      </c>
+      <c r="AC319" t="n">
+        <v>346.23</v>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -30760,7 +31048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B320"/>
+  <dimension ref="A1:B323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33963,6 +34251,36 @@
       </c>
       <c r="B320" t="n">
         <v>1.71</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>
@@ -34131,28 +34449,28 @@
         <v>0.099</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6995978274245814</v>
+        <v>-0.6826798514589928</v>
       </c>
       <c r="J2" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K2" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4139008313813271</v>
+        <v>0.4010486848597044</v>
       </c>
       <c r="M2" t="n">
-        <v>4.790065380439411</v>
+        <v>4.847460896078389</v>
       </c>
       <c r="N2" t="n">
-        <v>35.94815642174086</v>
+        <v>36.42194367284783</v>
       </c>
       <c r="O2" t="n">
-        <v>5.995678145276051</v>
+        <v>6.035059541781492</v>
       </c>
       <c r="P2" t="n">
-        <v>367.6057014544216</v>
+        <v>367.4226758561652</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34209,28 +34527,28 @@
         <v>0.1919</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5535189561515231</v>
+        <v>-0.5514377057924087</v>
       </c>
       <c r="J3" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K3" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3367710184041715</v>
+        <v>0.3390736638493944</v>
       </c>
       <c r="M3" t="n">
-        <v>4.466508736662615</v>
+        <v>4.436395057972623</v>
       </c>
       <c r="N3" t="n">
-        <v>31.29671063764912</v>
+        <v>31.01604637487772</v>
       </c>
       <c r="O3" t="n">
-        <v>5.594346310128568</v>
+        <v>5.569205183406131</v>
       </c>
       <c r="P3" t="n">
-        <v>351.0498382335993</v>
+        <v>351.0273288368238</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34287,28 +34605,28 @@
         <v>0.1119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3803311754419447</v>
+        <v>-0.3674410786143934</v>
       </c>
       <c r="J4" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K4" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3318568465927851</v>
+        <v>0.31399526937126</v>
       </c>
       <c r="M4" t="n">
-        <v>2.970559896512564</v>
+        <v>3.025002982763918</v>
       </c>
       <c r="N4" t="n">
-        <v>15.10593124341707</v>
+        <v>15.43525971889344</v>
       </c>
       <c r="O4" t="n">
-        <v>3.886634951139233</v>
+        <v>3.928773309685027</v>
       </c>
       <c r="P4" t="n">
-        <v>339.875542772592</v>
+        <v>339.7360922491372</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34365,28 +34683,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1298575665778747</v>
+        <v>-0.113303457520215</v>
       </c>
       <c r="J5" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K5" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0460888458292954</v>
+        <v>0.03466186404414417</v>
       </c>
       <c r="M5" t="n">
-        <v>3.12224775730084</v>
+        <v>3.176139851711247</v>
       </c>
       <c r="N5" t="n">
-        <v>18.10304066892233</v>
+        <v>18.70890613251252</v>
       </c>
       <c r="O5" t="n">
-        <v>4.254766817220696</v>
+        <v>4.32537930504511</v>
       </c>
       <c r="P5" t="n">
-        <v>327.1573792051611</v>
+        <v>326.9782849576602</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34443,28 +34761,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1815432370870867</v>
+        <v>-0.1623002725651992</v>
       </c>
       <c r="J6" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K6" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04999246049246031</v>
+        <v>0.0398302919163549</v>
       </c>
       <c r="M6" t="n">
-        <v>4.608360576519449</v>
+        <v>4.653687189893653</v>
       </c>
       <c r="N6" t="n">
-        <v>32.48535386809351</v>
+        <v>33.22825471306391</v>
       </c>
       <c r="O6" t="n">
-        <v>5.699592429998264</v>
+        <v>5.764395433439999</v>
       </c>
       <c r="P6" t="n">
-        <v>322.3253654572754</v>
+        <v>322.1171802080425</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34521,28 +34839,28 @@
         <v>0.0725</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4282592094492178</v>
+        <v>-0.4091403619883016</v>
       </c>
       <c r="J7" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K7" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1405560248323383</v>
+        <v>0.1299333063794239</v>
       </c>
       <c r="M7" t="n">
-        <v>6.254254282660254</v>
+        <v>6.292816756963668</v>
       </c>
       <c r="N7" t="n">
-        <v>58.16830907965647</v>
+        <v>58.65583554808037</v>
       </c>
       <c r="O7" t="n">
-        <v>7.626815133439152</v>
+        <v>7.658709783513172</v>
       </c>
       <c r="P7" t="n">
-        <v>324.7588963421355</v>
+        <v>324.5520566568769</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34599,28 +34917,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5176275240555658</v>
+        <v>-0.504563683697331</v>
       </c>
       <c r="J8" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K8" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1536066476888599</v>
+        <v>0.1485810376736358</v>
       </c>
       <c r="M8" t="n">
-        <v>6.973981440950771</v>
+        <v>6.979362861991683</v>
       </c>
       <c r="N8" t="n">
-        <v>76.57762041102129</v>
+        <v>76.33899356151265</v>
       </c>
       <c r="O8" t="n">
-        <v>8.750863980831909</v>
+        <v>8.737218868811325</v>
       </c>
       <c r="P8" t="n">
-        <v>329.6522541810081</v>
+        <v>329.5109211674448</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34677,28 +34995,28 @@
         <v>0.0678</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5651240563860401</v>
+        <v>-0.5551554659405153</v>
       </c>
       <c r="J9" t="n">
+        <v>318</v>
+      </c>
+      <c r="K9" t="n">
         <v>315</v>
       </c>
-      <c r="K9" t="n">
-        <v>312</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1525657509207462</v>
+        <v>0.1499387398193659</v>
       </c>
       <c r="M9" t="n">
-        <v>7.491066485432836</v>
+        <v>7.471673095978024</v>
       </c>
       <c r="N9" t="n">
-        <v>91.97683867807559</v>
+        <v>91.38383020967413</v>
       </c>
       <c r="O9" t="n">
-        <v>9.590455603258668</v>
+        <v>9.559489014046417</v>
       </c>
       <c r="P9" t="n">
-        <v>336.807424972054</v>
+        <v>336.6992268068394</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34755,28 +35073,28 @@
         <v>0.0693</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5509191070980126</v>
+        <v>-0.5477551022684536</v>
       </c>
       <c r="J10" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K10" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1578098960690217</v>
+        <v>0.158661212380847</v>
       </c>
       <c r="M10" t="n">
-        <v>7.365876289292224</v>
+        <v>7.313705849843259</v>
       </c>
       <c r="N10" t="n">
-        <v>83.81021819105671</v>
+        <v>83.04362110399632</v>
       </c>
       <c r="O10" t="n">
-        <v>9.154792088903861</v>
+        <v>9.112827283779515</v>
       </c>
       <c r="P10" t="n">
-        <v>348.1353377693406</v>
+        <v>348.1009801326618</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34833,28 +35151,28 @@
         <v>0.076</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.461721926074001</v>
+        <v>-0.4534463306638761</v>
       </c>
       <c r="J11" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K11" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08406923299339186</v>
+        <v>0.08257532751135976</v>
       </c>
       <c r="M11" t="n">
-        <v>8.823607953720769</v>
+        <v>8.784138848971455</v>
       </c>
       <c r="N11" t="n">
-        <v>119.5450855791189</v>
+        <v>118.6186656153496</v>
       </c>
       <c r="O11" t="n">
-        <v>10.93366752645785</v>
+        <v>10.89121965692317</v>
       </c>
       <c r="P11" t="n">
-        <v>354.3702623697004</v>
+        <v>354.2802158163342</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34911,28 +35229,28 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4248332650710692</v>
+        <v>-0.4220218947827672</v>
       </c>
       <c r="J12" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K12" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06756935305189771</v>
+        <v>0.06787183890078241</v>
       </c>
       <c r="M12" t="n">
-        <v>9.014090187039079</v>
+        <v>8.944532223779337</v>
       </c>
       <c r="N12" t="n">
-        <v>129.1839980506484</v>
+        <v>127.9942619414609</v>
       </c>
       <c r="O12" t="n">
-        <v>11.3659138678176</v>
+        <v>11.3134549073862</v>
       </c>
       <c r="P12" t="n">
-        <v>359.8152878853783</v>
+        <v>359.7848585910669</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34989,28 +35307,28 @@
         <v>0.0576</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.581664965417317</v>
+        <v>-0.5773589335894401</v>
       </c>
       <c r="J13" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K13" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1025078152231229</v>
+        <v>0.1027966986377897</v>
       </c>
       <c r="M13" t="n">
-        <v>9.762225088387989</v>
+        <v>9.692061303071609</v>
       </c>
       <c r="N13" t="n">
-        <v>152.4630762496216</v>
+        <v>151.0722215454597</v>
       </c>
       <c r="O13" t="n">
-        <v>12.34759394577023</v>
+        <v>12.2911440291561</v>
       </c>
       <c r="P13" t="n">
-        <v>366.15241341324</v>
+        <v>366.1055669163462</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35067,28 +35385,28 @@
         <v>0.067</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4844879401419416</v>
+        <v>-0.5028657702495575</v>
       </c>
       <c r="J14" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K14" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06933194846123569</v>
+        <v>0.07515492101846521</v>
       </c>
       <c r="M14" t="n">
-        <v>9.850213108599039</v>
+        <v>9.856225622001263</v>
       </c>
       <c r="N14" t="n">
-        <v>162.170744162153</v>
+        <v>161.5834423521654</v>
       </c>
       <c r="O14" t="n">
-        <v>12.73462775907302</v>
+        <v>12.71154759862722</v>
       </c>
       <c r="P14" t="n">
-        <v>369.5551705811357</v>
+        <v>369.755107113108</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35145,28 +35463,28 @@
         <v>0.074</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8538068299338432</v>
+        <v>-0.9159983970824331</v>
       </c>
       <c r="J15" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K15" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L15" t="n">
-        <v>0.200001061155424</v>
+        <v>0.2145403498205629</v>
       </c>
       <c r="M15" t="n">
-        <v>9.283611792524828</v>
+        <v>9.582946197971594</v>
       </c>
       <c r="N15" t="n">
-        <v>150.0795530262568</v>
+        <v>159.5090992337708</v>
       </c>
       <c r="O15" t="n">
-        <v>12.2506960221147</v>
+        <v>12.62969117729214</v>
       </c>
       <c r="P15" t="n">
-        <v>380.0145386832652</v>
+        <v>380.691134917879</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35223,28 +35541,28 @@
         <v>0.0895</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6502244387457538</v>
+        <v>-0.5909484094052611</v>
       </c>
       <c r="J16" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K16" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1327192932602634</v>
+        <v>0.1061151546416861</v>
       </c>
       <c r="M16" t="n">
-        <v>9.094159022877227</v>
+        <v>9.288417362115375</v>
       </c>
       <c r="N16" t="n">
-        <v>140.0695421873686</v>
+        <v>150.4786202844319</v>
       </c>
       <c r="O16" t="n">
-        <v>11.83509789513245</v>
+        <v>12.26697274328234</v>
       </c>
       <c r="P16" t="n">
-        <v>375.3639069323743</v>
+        <v>374.7134815323072</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35301,28 +35619,28 @@
         <v>0.0617</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8452962741021289</v>
+        <v>-0.856412009505138</v>
       </c>
       <c r="J17" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K17" t="n">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1274118790438886</v>
+        <v>0.132303732805988</v>
       </c>
       <c r="M17" t="n">
-        <v>12.26416211109829</v>
+        <v>12.21478939128751</v>
       </c>
       <c r="N17" t="n">
-        <v>250.2135257658302</v>
+        <v>248.1651761054479</v>
       </c>
       <c r="O17" t="n">
-        <v>15.81813913726359</v>
+        <v>15.75325922168006</v>
       </c>
       <c r="P17" t="n">
-        <v>377.9378518104803</v>
+        <v>378.0592792695177</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35379,28 +35697,28 @@
         <v>0.0469</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3984534504973852</v>
+        <v>-0.421239837383806</v>
       </c>
       <c r="J18" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K18" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04610751256925016</v>
+        <v>0.05172481929636119</v>
       </c>
       <c r="M18" t="n">
-        <v>10.21358017019362</v>
+        <v>10.2524627622063</v>
       </c>
       <c r="N18" t="n">
-        <v>169.3815425446441</v>
+        <v>169.240512223538</v>
       </c>
       <c r="O18" t="n">
-        <v>13.01466644000699</v>
+        <v>13.00924718127602</v>
       </c>
       <c r="P18" t="n">
-        <v>375.7264803474293</v>
+        <v>375.9741145642284</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35457,28 +35775,28 @@
         <v>0.0659</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1805513451643897</v>
+        <v>-0.2039184052526059</v>
       </c>
       <c r="J19" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K19" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L19" t="n">
-        <v>0.009690311296159382</v>
+        <v>0.01244292373777434</v>
       </c>
       <c r="M19" t="n">
-        <v>10.74819970479599</v>
+        <v>10.77388516404014</v>
       </c>
       <c r="N19" t="n">
-        <v>171.0899892725442</v>
+        <v>170.9973722867314</v>
       </c>
       <c r="O19" t="n">
-        <v>13.08013720388835</v>
+        <v>13.07659635710804</v>
       </c>
       <c r="P19" t="n">
-        <v>368.7277593735275</v>
+        <v>368.9822876576073</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35535,28 +35853,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.01342714976614979</v>
+        <v>-0.01592658187008476</v>
       </c>
       <c r="J20" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K20" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L20" t="n">
-        <v>4.615462813417626e-05</v>
+        <v>6.612740674083462e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>11.41451285656303</v>
+        <v>11.32017482684782</v>
       </c>
       <c r="N20" t="n">
-        <v>202.598990319456</v>
+        <v>200.71021070026</v>
       </c>
       <c r="O20" t="n">
-        <v>14.23372721108059</v>
+        <v>14.16722311182611</v>
       </c>
       <c r="P20" t="n">
-        <v>360.7626099303899</v>
+        <v>360.7896612231144</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -35613,28 +35931,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.03371753689163901</v>
+        <v>0.04001713470657059</v>
       </c>
       <c r="J21" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K21" t="n">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0003394501350050261</v>
+        <v>0.0004865763752668339</v>
       </c>
       <c r="M21" t="n">
-        <v>10.39863053300328</v>
+        <v>10.32714891260711</v>
       </c>
       <c r="N21" t="n">
-        <v>171.8371382579003</v>
+        <v>170.3090283081696</v>
       </c>
       <c r="O21" t="n">
-        <v>13.10866653240902</v>
+        <v>13.05025012435278</v>
       </c>
       <c r="P21" t="n">
-        <v>358.6806773839336</v>
+        <v>358.6118380176431</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -35691,28 +36009,28 @@
         <v>0.0557</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1750856119362574</v>
+        <v>0.1831467052491516</v>
       </c>
       <c r="J22" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K22" t="n">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="L22" t="n">
-        <v>0.008340851470451716</v>
+        <v>0.00927663610679641</v>
       </c>
       <c r="M22" t="n">
-        <v>10.98206614794229</v>
+        <v>10.9125863692926</v>
       </c>
       <c r="N22" t="n">
-        <v>187.0603457942265</v>
+        <v>185.4676566952953</v>
       </c>
       <c r="O22" t="n">
-        <v>13.6770006139587</v>
+        <v>13.61865106004612</v>
       </c>
       <c r="P22" t="n">
-        <v>353.5523579902678</v>
+        <v>353.4642781155936</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -35769,28 +36087,28 @@
         <v>0.0982</v>
       </c>
       <c r="I23" t="n">
-        <v>0.08917575074384088</v>
+        <v>0.09938938510457895</v>
       </c>
       <c r="J23" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K23" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L23" t="n">
-        <v>0.001977285325246325</v>
+        <v>0.002496809957219126</v>
       </c>
       <c r="M23" t="n">
-        <v>11.61466420182879</v>
+        <v>11.55643125564142</v>
       </c>
       <c r="N23" t="n">
-        <v>206.1362988526509</v>
+        <v>204.4775494567206</v>
       </c>
       <c r="O23" t="n">
-        <v>14.35744750478479</v>
+        <v>14.29956465969229</v>
       </c>
       <c r="P23" t="n">
-        <v>347.9496478626364</v>
+        <v>347.8383983481323</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -35847,28 +36165,28 @@
         <v>0.0843</v>
       </c>
       <c r="I24" t="n">
-        <v>0.05096449806537934</v>
+        <v>0.06695005623974293</v>
       </c>
       <c r="J24" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K24" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0008289161115121457</v>
+        <v>0.001449458600753295</v>
       </c>
       <c r="M24" t="n">
-        <v>9.809092659068096</v>
+        <v>9.796110063443248</v>
       </c>
       <c r="N24" t="n">
-        <v>160.7883659726624</v>
+        <v>159.9937238908848</v>
       </c>
       <c r="O24" t="n">
-        <v>12.68023524910569</v>
+        <v>12.64886255324505</v>
       </c>
       <c r="P24" t="n">
-        <v>347.1704717318237</v>
+        <v>346.9963683810135</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -35925,28 +36243,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.02586357918660933</v>
+        <v>-0.002438149024571652</v>
       </c>
       <c r="J25" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K25" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0001974184996066386</v>
+        <v>1.771034216946354e-06</v>
       </c>
       <c r="M25" t="n">
-        <v>10.42403238576437</v>
+        <v>10.46273903659718</v>
       </c>
       <c r="N25" t="n">
-        <v>173.9776662241927</v>
+        <v>173.9120168649397</v>
       </c>
       <c r="O25" t="n">
-        <v>13.19005937151887</v>
+        <v>13.18757054445358</v>
       </c>
       <c r="P25" t="n">
-        <v>342.8004226424995</v>
+        <v>342.5452968027835</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -36003,28 +36321,28 @@
         <v>0.0467</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2177404123745546</v>
+        <v>0.2348382406036078</v>
       </c>
       <c r="J26" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K26" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01127674038222348</v>
+        <v>0.0132770600925245</v>
       </c>
       <c r="M26" t="n">
-        <v>11.77585186089773</v>
+        <v>11.7547765712281</v>
       </c>
       <c r="N26" t="n">
-        <v>215.612613138737</v>
+        <v>214.4694616215746</v>
       </c>
       <c r="O26" t="n">
-        <v>14.68375337366904</v>
+        <v>14.64477591571734</v>
       </c>
       <c r="P26" t="n">
-        <v>338.8268440489849</v>
+        <v>338.6419059487899</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -36081,28 +36399,28 @@
         <v>0.0484</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1534580418176676</v>
+        <v>-0.1319401085122745</v>
       </c>
       <c r="J27" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K27" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L27" t="n">
-        <v>0.004091921468179383</v>
+        <v>0.003070029745536274</v>
       </c>
       <c r="M27" t="n">
-        <v>12.03184215961532</v>
+        <v>12.01987287755332</v>
       </c>
       <c r="N27" t="n">
-        <v>297.2871799317599</v>
+        <v>295.8082376817815</v>
       </c>
       <c r="O27" t="n">
-        <v>17.24201786136878</v>
+        <v>17.19907665201192</v>
       </c>
       <c r="P27" t="n">
-        <v>339.9572429149578</v>
+        <v>339.7244561110407</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -36159,28 +36477,28 @@
         <v>0.0576</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.246700251495748</v>
+        <v>-0.2342371239970477</v>
       </c>
       <c r="J28" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K28" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02246327345556487</v>
+        <v>0.0205969477304484</v>
       </c>
       <c r="M28" t="n">
-        <v>9.319964311151434</v>
+        <v>9.300744121525716</v>
       </c>
       <c r="N28" t="n">
-        <v>137.3738707481474</v>
+        <v>136.5226035341176</v>
       </c>
       <c r="O28" t="n">
-        <v>11.7206599962693</v>
+        <v>11.68428874746416</v>
       </c>
       <c r="P28" t="n">
-        <v>348.9419669527829</v>
+        <v>348.8071259187585</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -36237,28 +36555,28 @@
         <v>0.2</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1902246681217626</v>
+        <v>0.1812771462893725</v>
       </c>
       <c r="J29" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K29" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L29" t="n">
-        <v>0.006288899423177785</v>
+        <v>0.005818885669904628</v>
       </c>
       <c r="M29" t="n">
-        <v>10.21096464638472</v>
+        <v>10.15670474396733</v>
       </c>
       <c r="N29" t="n">
-        <v>291.6737779886582</v>
+        <v>289.1168299752541</v>
       </c>
       <c r="O29" t="n">
-        <v>17.0784594735198</v>
+        <v>17.0034358285393</v>
       </c>
       <c r="P29" t="n">
-        <v>343.9373078305259</v>
+        <v>344.0348044467125</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -36296,7 +36614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD316"/>
+  <dimension ref="A1:AD319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83957,7 +84275,7 @@
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>-38.37545047292575,174.65977592095328</t>
+          <t>-38.37543800561169,174.65972069029453</t>
         </is>
       </c>
       <c r="Q315" t="inlineStr">
@@ -84109,7 +84427,7 @@
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>-38.375478884395086,174.65990178531092</t>
+          <t>-38.37545807251057,174.6598095874593</t>
         </is>
       </c>
       <c r="Q316" t="inlineStr">
@@ -84180,6 +84498,462 @@
       <c r="AD316" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:49+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>-38.38454322567864,174.65502344063003</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>-38.38398995734783,174.6556325558324</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>-38.38335943058973,174.65603281150842</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-38.382742501524696,174.65646984459</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-38.38212702282252,174.65691081372788</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>-38.38150851118248,174.657343597964</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>-38.38087819176559,174.65774447389117</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>-38.38022955068895,174.65809583097848</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>-38.37955726172996,174.6584114197319</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>-38.37885696781775,174.65862056462967</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>-38.37816988325893,174.65883774277867</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>-38.37748493630447,174.65904967670892</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>-38.37682678064753,174.65938032656018</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>-38.376210242146165,174.6598953727209</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>-38.37545995998763,174.65981794907623</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>-38.37479827666621,174.66012639568882</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>-38.374124090481175,174.66037707375065</t>
+        </is>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>-38.3734733569613,174.6607199436697</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>-38.37278943751114,174.66095169772254</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>-38.372120999733156,174.66123621628716</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>-38.37146316873882,174.66155542115393</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>-38.370828360011096,174.6619567343652</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>-38.37015947787224,174.66223877629864</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>-38.369501648336865,174.6625600373887</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>-38.36884311400571,174.66287882026475</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>-38.368207023409944,174.6632809172438</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>-38.36753869572127,174.66356874043893</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>-38.36689482367452,174.66395003918802</t>
+        </is>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>-38.38454322567864,174.65502344063003</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>-38.38398995734783,174.6556325558324</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>-38.38335943058973,174.65603281150842</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-38.382742501524696,174.65646984459</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-38.38212702282252,174.65691081372788</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>-38.38150851118248,174.657343597964</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>-38.38087819176559,174.65774447389117</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>-38.38022955068895,174.65809583097848</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>-38.37955726172996,174.6584114197319</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>-38.37884945715296,174.6585908092302</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>-38.37816633174797,174.6588220091716</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>-38.37748493630447,174.65904967670892</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>-38.37682678064753,174.65938032656018</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>-38.376210242146165,174.6598953727209</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>-38.375339234739286,174.659283136492</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>-38.37479600824863,174.66011710363796</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>-38.3741263103778,174.66038506004998</t>
+        </is>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>-38.37347474113697,174.66072466263145</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>-38.372794219194205,174.66096799944313</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>-38.372124301433956,174.66124747791872</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>-38.37147006092969,174.66157939470764</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>-38.370827782774164,174.6619546872041</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>-38.370165159070076,174.66225892450012</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>-38.36951422588294,174.66260464319686</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>-38.36885854723067,174.6629335535031</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>-38.36821546991646,174.66331232398508</t>
+        </is>
+      </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>-38.36754132281658,174.66357908774162</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>-38.366881185103615,174.66389586400516</t>
+        </is>
+      </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-38.38454678943433,174.65503307550364</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>-38.38399405753886,174.6556436410565</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>-38.3833619979844,174.656039752671</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-38.382743037991695,174.6564712949717</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-38.38212709946016,174.65691102092381</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>-38.38151012056213,174.6573479490468</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>-38.38087922636083,174.65774727099472</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>-38.38022771141678,174.6580908583901</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>-38.37955530716586,174.65840538639432</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>-38.37885132794198,174.65859822083098</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>-38.3781649906174,174.65881606780982</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>-38.37748493630447,174.65904967670892</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>-38.37682678064753,174.65938032656018</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>-38.376210242146165,174.6598953727209</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>-38.375339234739286,174.659283136492</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>-38.37479600824863,174.66011710363796</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>-38.3741263103778,174.66038506004998</t>
+        </is>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>-38.37347474113697,174.66072466263145</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>-38.372794219194205,174.66096799944313</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>-38.372124301433956,174.66124747791872</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>-38.371470988129865,174.66158261984972</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>-38.37082939296127,174.6619603977062</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>-38.37016783257371,174.66226840600777</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>-38.36951705127133,174.66261466334421</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>-38.368860461191794,174.66294034128813</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>-38.36821159617488,174.66329792020287</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>-38.367536621698015,174.66356057151626</t>
+        </is>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>-38.36687937394338,174.66388866971673</t>
+        </is>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0257/nzd0257.xlsx
+++ b/data/nzd0257/nzd0257.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD319"/>
+  <dimension ref="A1:AD320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30894,7 +30894,7 @@
         <v>323.44</v>
       </c>
       <c r="P318" t="n">
-        <v>402.55</v>
+        <v>353.94</v>
       </c>
       <c r="Q318" t="n">
         <v>350.15</v>
@@ -30990,7 +30990,7 @@
         <v>323.44</v>
       </c>
       <c r="P319" t="n">
-        <v>402.55</v>
+        <v>353.94</v>
       </c>
       <c r="Q319" t="n">
         <v>350.15</v>
@@ -31034,6 +31034,102 @@
       <c r="AD319" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>357.17</v>
+      </c>
+      <c r="C320" t="n">
+        <v>337.77</v>
+      </c>
+      <c r="D320" t="n">
+        <v>334.26</v>
+      </c>
+      <c r="E320" t="n">
+        <v>332.38</v>
+      </c>
+      <c r="F320" t="n">
+        <v>327.21</v>
+      </c>
+      <c r="G320" t="n">
+        <v>324.06</v>
+      </c>
+      <c r="H320" t="n">
+        <v>325.78</v>
+      </c>
+      <c r="I320" t="n">
+        <v>330.18</v>
+      </c>
+      <c r="J320" t="n">
+        <v>334.64</v>
+      </c>
+      <c r="K320" t="n">
+        <v>347.55</v>
+      </c>
+      <c r="L320" t="n">
+        <v>351.41</v>
+      </c>
+      <c r="M320" t="n">
+        <v>354.27</v>
+      </c>
+      <c r="N320" t="n">
+        <v>350.51</v>
+      </c>
+      <c r="O320" t="n">
+        <v>345.33</v>
+      </c>
+      <c r="P320" t="n">
+        <v>368.25</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>351.78</v>
+      </c>
+      <c r="R320" t="n">
+        <v>354.23</v>
+      </c>
+      <c r="S320" t="n">
+        <v>354.43</v>
+      </c>
+      <c r="T320" t="n">
+        <v>358.41</v>
+      </c>
+      <c r="U320" t="n">
+        <v>360.31</v>
+      </c>
+      <c r="V320" t="n">
+        <v>359.25</v>
+      </c>
+      <c r="W320" t="n">
+        <v>356.73</v>
+      </c>
+      <c r="X320" t="n">
+        <v>356.12</v>
+      </c>
+      <c r="Y320" t="n">
+        <v>348.57</v>
+      </c>
+      <c r="Z320" t="n">
+        <v>343.73</v>
+      </c>
+      <c r="AA320" t="n">
+        <v>344.67</v>
+      </c>
+      <c r="AB320" t="n">
+        <v>351.67</v>
+      </c>
+      <c r="AC320" t="n">
+        <v>350.81</v>
+      </c>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -31048,7 +31144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B323"/>
+  <dimension ref="A1:B324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34281,6 +34377,16 @@
       </c>
       <c r="B323" t="n">
         <v>1.12</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -34449,28 +34555,28 @@
         <v>0.099</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6826798514589928</v>
+        <v>-0.6781330030896769</v>
       </c>
       <c r="J2" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K2" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4010486848597044</v>
+        <v>0.3981170960948885</v>
       </c>
       <c r="M2" t="n">
-        <v>4.847460896078389</v>
+        <v>4.860063508136913</v>
       </c>
       <c r="N2" t="n">
-        <v>36.42194367284783</v>
+        <v>36.48642779248016</v>
       </c>
       <c r="O2" t="n">
-        <v>6.035059541781492</v>
+        <v>6.040399638474275</v>
       </c>
       <c r="P2" t="n">
-        <v>367.4226758561652</v>
+        <v>367.3732770990044</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34527,28 +34633,28 @@
         <v>0.1919</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5514377057924087</v>
+        <v>-0.5507446273297031</v>
       </c>
       <c r="J3" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K3" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3390736638493944</v>
+        <v>0.3398371457107554</v>
       </c>
       <c r="M3" t="n">
-        <v>4.436395057972623</v>
+        <v>4.426442275341498</v>
       </c>
       <c r="N3" t="n">
-        <v>31.01604637487772</v>
+        <v>30.92296855401377</v>
       </c>
       <c r="O3" t="n">
-        <v>5.569205183406131</v>
+        <v>5.560842432043348</v>
       </c>
       <c r="P3" t="n">
-        <v>351.0273288368238</v>
+        <v>351.0197989585672</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34605,28 +34711,28 @@
         <v>0.1119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3674410786143934</v>
+        <v>-0.3649653820290573</v>
       </c>
       <c r="J4" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K4" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L4" t="n">
-        <v>0.31399526937126</v>
+        <v>0.3116515549886832</v>
       </c>
       <c r="M4" t="n">
-        <v>3.025002982763918</v>
+        <v>3.031401202443845</v>
       </c>
       <c r="N4" t="n">
-        <v>15.43525971889344</v>
+        <v>15.43983966753335</v>
       </c>
       <c r="O4" t="n">
-        <v>3.928773309685027</v>
+        <v>3.929356139055526</v>
       </c>
       <c r="P4" t="n">
-        <v>339.7360922491372</v>
+        <v>339.7091953032773</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34683,28 +34789,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.113303457520215</v>
+        <v>-0.1082891891270307</v>
       </c>
       <c r="J5" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K5" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03466186404414417</v>
+        <v>0.03158753593573793</v>
       </c>
       <c r="M5" t="n">
-        <v>3.176139851711247</v>
+        <v>3.192417995996529</v>
       </c>
       <c r="N5" t="n">
-        <v>18.70890613251252</v>
+        <v>18.86753779965509</v>
       </c>
       <c r="O5" t="n">
-        <v>4.32537930504511</v>
+        <v>4.343677911592328</v>
       </c>
       <c r="P5" t="n">
-        <v>326.9782849576602</v>
+        <v>326.9238079646807</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34761,28 +34867,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1623002725651992</v>
+        <v>-0.1567019186430925</v>
       </c>
       <c r="J6" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K6" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0398302919163549</v>
+        <v>0.03715561703251646</v>
       </c>
       <c r="M6" t="n">
-        <v>4.653687189893653</v>
+        <v>4.665977376939886</v>
       </c>
       <c r="N6" t="n">
-        <v>33.22825471306391</v>
+        <v>33.39493904205742</v>
       </c>
       <c r="O6" t="n">
-        <v>5.764395433439999</v>
+        <v>5.778835439953055</v>
       </c>
       <c r="P6" t="n">
-        <v>322.1171802080425</v>
+        <v>322.0563574791025</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34839,28 +34945,28 @@
         <v>0.0725</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4091403619883016</v>
+        <v>-0.4030259502599881</v>
       </c>
       <c r="J7" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K7" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1299333063794239</v>
+        <v>0.126626781955142</v>
       </c>
       <c r="M7" t="n">
-        <v>6.292816756963668</v>
+        <v>6.304378095795464</v>
       </c>
       <c r="N7" t="n">
-        <v>58.65583554808037</v>
+        <v>58.79504475565667</v>
       </c>
       <c r="O7" t="n">
-        <v>7.658709783513172</v>
+        <v>7.667792691228465</v>
       </c>
       <c r="P7" t="n">
-        <v>324.5520566568769</v>
+        <v>324.4856272720339</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34917,28 +35023,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.504563683697331</v>
+        <v>-0.4988961852372381</v>
       </c>
       <c r="J8" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K8" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1485810376736358</v>
+        <v>0.1460464223981331</v>
       </c>
       <c r="M8" t="n">
-        <v>6.979362861991683</v>
+        <v>6.988122200319373</v>
       </c>
       <c r="N8" t="n">
-        <v>76.33899356151265</v>
+        <v>76.37726624470319</v>
       </c>
       <c r="O8" t="n">
-        <v>8.737218868811325</v>
+        <v>8.739408804072687</v>
       </c>
       <c r="P8" t="n">
-        <v>329.5109211674448</v>
+        <v>329.4493472249248</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34995,28 +35101,28 @@
         <v>0.0678</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5551554659405153</v>
+        <v>-0.5503545527688757</v>
       </c>
       <c r="J9" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K9" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1499387398193659</v>
+        <v>0.148222593500772</v>
       </c>
       <c r="M9" t="n">
-        <v>7.471673095978024</v>
+        <v>7.472755521884565</v>
       </c>
       <c r="N9" t="n">
-        <v>91.38383020967413</v>
+        <v>91.29441580713608</v>
       </c>
       <c r="O9" t="n">
-        <v>9.559489014046417</v>
+        <v>9.554811134037976</v>
       </c>
       <c r="P9" t="n">
-        <v>336.6992268068394</v>
+        <v>336.6468979266749</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35073,28 +35179,28 @@
         <v>0.0693</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5477551022684536</v>
+        <v>-0.5472417470239738</v>
       </c>
       <c r="J10" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K10" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L10" t="n">
-        <v>0.158661212380847</v>
+        <v>0.1592146504415688</v>
       </c>
       <c r="M10" t="n">
-        <v>7.313705849843259</v>
+        <v>7.293497967046528</v>
       </c>
       <c r="N10" t="n">
-        <v>83.04362110399632</v>
+        <v>82.78392979875942</v>
       </c>
       <c r="O10" t="n">
-        <v>9.112827283779515</v>
+        <v>9.098567458603547</v>
       </c>
       <c r="P10" t="n">
-        <v>348.1009801326618</v>
+        <v>348.095382714101</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35151,28 +35257,28 @@
         <v>0.076</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4534463306638761</v>
+        <v>-0.4503588198479259</v>
       </c>
       <c r="J11" t="n">
+        <v>319</v>
+      </c>
+      <c r="K11" t="n">
         <v>318</v>
       </c>
-      <c r="K11" t="n">
-        <v>317</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.08257532751135976</v>
+        <v>0.08194987957769539</v>
       </c>
       <c r="M11" t="n">
-        <v>8.784138848971455</v>
+        <v>8.772752295720483</v>
       </c>
       <c r="N11" t="n">
-        <v>118.6186656153496</v>
+        <v>118.3271976067803</v>
       </c>
       <c r="O11" t="n">
-        <v>10.89121965692317</v>
+        <v>10.87783055607966</v>
       </c>
       <c r="P11" t="n">
-        <v>354.2802158163342</v>
+        <v>354.2464851104984</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35229,28 +35335,28 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4220218947827672</v>
+        <v>-0.4204323542195237</v>
       </c>
       <c r="J12" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K12" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06787183890078241</v>
+        <v>0.06776665443285912</v>
       </c>
       <c r="M12" t="n">
-        <v>8.944532223779337</v>
+        <v>8.925152015660439</v>
       </c>
       <c r="N12" t="n">
-        <v>127.9942619414609</v>
+        <v>127.6148607685332</v>
       </c>
       <c r="O12" t="n">
-        <v>11.3134549073862</v>
+        <v>11.29667476598903</v>
       </c>
       <c r="P12" t="n">
-        <v>359.7848585910669</v>
+        <v>359.7675891943546</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35307,28 +35413,28 @@
         <v>0.0576</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5773589335894401</v>
+        <v>-0.5753959826312915</v>
       </c>
       <c r="J13" t="n">
+        <v>319</v>
+      </c>
+      <c r="K13" t="n">
         <v>318</v>
       </c>
-      <c r="K13" t="n">
-        <v>317</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1027966986377897</v>
+        <v>0.1027081131998077</v>
       </c>
       <c r="M13" t="n">
-        <v>9.692061303071609</v>
+        <v>9.671679477137594</v>
       </c>
       <c r="N13" t="n">
-        <v>151.0722215454597</v>
+        <v>150.6301132537527</v>
       </c>
       <c r="O13" t="n">
-        <v>12.2911440291561</v>
+        <v>12.27314602103929</v>
       </c>
       <c r="P13" t="n">
-        <v>366.1055669163462</v>
+        <v>366.0841218995394</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35385,28 +35491,28 @@
         <v>0.067</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5028657702495575</v>
+        <v>-0.5065523780779063</v>
       </c>
       <c r="J14" t="n">
+        <v>319</v>
+      </c>
+      <c r="K14" t="n">
         <v>318</v>
       </c>
-      <c r="K14" t="n">
-        <v>317</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.07515492101846521</v>
+        <v>0.07655385982160889</v>
       </c>
       <c r="M14" t="n">
-        <v>9.856225622001263</v>
+        <v>9.845087800543848</v>
       </c>
       <c r="N14" t="n">
-        <v>161.5834423521654</v>
+        <v>161.1915817415823</v>
       </c>
       <c r="O14" t="n">
-        <v>12.71154759862722</v>
+        <v>12.69612467415086</v>
       </c>
       <c r="P14" t="n">
-        <v>369.755107113108</v>
+        <v>369.7953828859239</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35463,28 +35569,28 @@
         <v>0.074</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9159983970824331</v>
+        <v>-0.922894221459275</v>
       </c>
       <c r="J15" t="n">
+        <v>319</v>
+      </c>
+      <c r="K15" t="n">
         <v>318</v>
       </c>
-      <c r="K15" t="n">
-        <v>317</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.2145403498205629</v>
+        <v>0.2176767444055909</v>
       </c>
       <c r="M15" t="n">
-        <v>9.582946197971594</v>
+        <v>9.596783993932856</v>
       </c>
       <c r="N15" t="n">
-        <v>159.5090992337708</v>
+        <v>159.4142801774277</v>
       </c>
       <c r="O15" t="n">
-        <v>12.62969117729214</v>
+        <v>12.62593680395351</v>
       </c>
       <c r="P15" t="n">
-        <v>380.691134917879</v>
+        <v>380.7664710178689</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35541,28 +35647,28 @@
         <v>0.0895</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5909484094052611</v>
+        <v>-0.6444173822702229</v>
       </c>
       <c r="J16" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K16" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1061151546416861</v>
+        <v>0.1333832105717612</v>
       </c>
       <c r="M16" t="n">
-        <v>9.288417362115375</v>
+        <v>9.036305182660801</v>
       </c>
       <c r="N16" t="n">
-        <v>150.4786202844319</v>
+        <v>138.4249764456862</v>
       </c>
       <c r="O16" t="n">
-        <v>12.26697274328234</v>
+        <v>11.76541441878212</v>
       </c>
       <c r="P16" t="n">
-        <v>374.7134815323072</v>
+        <v>375.3008142455798</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35619,28 +35725,28 @@
         <v>0.0617</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.856412009505138</v>
+        <v>-0.8587982509205349</v>
       </c>
       <c r="J17" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K17" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L17" t="n">
-        <v>0.132303732805988</v>
+        <v>0.1336304355203856</v>
       </c>
       <c r="M17" t="n">
-        <v>12.21478939128751</v>
+        <v>12.19056060449151</v>
       </c>
       <c r="N17" t="n">
-        <v>248.1651761054479</v>
+        <v>247.4252173728084</v>
       </c>
       <c r="O17" t="n">
-        <v>15.75325922168006</v>
+        <v>15.72975579507859</v>
       </c>
       <c r="P17" t="n">
-        <v>378.0592792695177</v>
+        <v>378.0854565123221</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35697,28 +35803,28 @@
         <v>0.0469</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.421239837383806</v>
+        <v>-0.4277126317243938</v>
       </c>
       <c r="J18" t="n">
+        <v>319</v>
+      </c>
+      <c r="K18" t="n">
         <v>318</v>
       </c>
-      <c r="K18" t="n">
-        <v>317</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.05172481929636119</v>
+        <v>0.05344000376039937</v>
       </c>
       <c r="M18" t="n">
-        <v>10.2524627622063</v>
+        <v>10.25874969545751</v>
       </c>
       <c r="N18" t="n">
-        <v>169.240512223538</v>
+        <v>169.0678040984485</v>
       </c>
       <c r="O18" t="n">
-        <v>13.00924718127602</v>
+        <v>13.00260758842043</v>
       </c>
       <c r="P18" t="n">
-        <v>375.9741145642284</v>
+        <v>376.0447529765296</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35775,28 +35881,28 @@
         <v>0.0659</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2039184052526059</v>
+        <v>-0.2094941629217727</v>
       </c>
       <c r="J19" t="n">
+        <v>319</v>
+      </c>
+      <c r="K19" t="n">
         <v>318</v>
       </c>
-      <c r="K19" t="n">
-        <v>317</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.01244292373777434</v>
+        <v>0.01318235425365655</v>
       </c>
       <c r="M19" t="n">
-        <v>10.77388516404014</v>
+        <v>10.77019340657715</v>
       </c>
       <c r="N19" t="n">
-        <v>170.9973722867314</v>
+        <v>170.7246528433675</v>
       </c>
       <c r="O19" t="n">
-        <v>13.07659635710804</v>
+        <v>13.06616442738141</v>
       </c>
       <c r="P19" t="n">
-        <v>368.9822876576073</v>
+        <v>369.0432757225108</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35853,28 +35959,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.01592658187008476</v>
+        <v>-0.01710288741281895</v>
       </c>
       <c r="J20" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K20" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L20" t="n">
-        <v>6.612740674083462e-05</v>
+        <v>7.671390698249514e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>11.32017482684782</v>
+        <v>11.2908996406618</v>
       </c>
       <c r="N20" t="n">
-        <v>200.71021070026</v>
+        <v>200.0929827257809</v>
       </c>
       <c r="O20" t="n">
-        <v>14.16722311182611</v>
+        <v>14.14542267752296</v>
       </c>
       <c r="P20" t="n">
-        <v>360.7896612231144</v>
+        <v>360.8024410712933</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -35931,28 +36037,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.04001713470657059</v>
+        <v>0.04041384176740632</v>
       </c>
       <c r="J21" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K21" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0004865763752668339</v>
+        <v>0.0004992759965424254</v>
       </c>
       <c r="M21" t="n">
-        <v>10.32714891260711</v>
+        <v>10.29609664333681</v>
       </c>
       <c r="N21" t="n">
-        <v>170.3090283081696</v>
+        <v>169.7697098282382</v>
       </c>
       <c r="O21" t="n">
-        <v>13.05025012435278</v>
+        <v>13.02957059262654</v>
       </c>
       <c r="P21" t="n">
-        <v>358.6118380176431</v>
+        <v>358.6074841758596</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36009,28 +36115,28 @@
         <v>0.0557</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1831467052491516</v>
+        <v>0.1837534001996571</v>
       </c>
       <c r="J22" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K22" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L22" t="n">
-        <v>0.00927663610679641</v>
+        <v>0.00939365726015795</v>
       </c>
       <c r="M22" t="n">
-        <v>10.9125863692926</v>
+        <v>10.88057647002874</v>
       </c>
       <c r="N22" t="n">
-        <v>185.4676566952953</v>
+        <v>184.882016464729</v>
       </c>
       <c r="O22" t="n">
-        <v>13.61865106004612</v>
+        <v>13.59713265599512</v>
       </c>
       <c r="P22" t="n">
-        <v>353.4642781155936</v>
+        <v>353.4576196663597</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36087,28 +36193,28 @@
         <v>0.0982</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09938938510457895</v>
+        <v>0.1031927069575492</v>
       </c>
       <c r="J23" t="n">
+        <v>319</v>
+      </c>
+      <c r="K23" t="n">
         <v>318</v>
       </c>
-      <c r="K23" t="n">
-        <v>317</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.002496809957219126</v>
+        <v>0.002705760595218987</v>
       </c>
       <c r="M23" t="n">
-        <v>11.55643125564142</v>
+        <v>11.53931439671782</v>
       </c>
       <c r="N23" t="n">
-        <v>204.4775494567206</v>
+        <v>203.957842416791</v>
       </c>
       <c r="O23" t="n">
-        <v>14.29956465969229</v>
+        <v>14.28138097022802</v>
       </c>
       <c r="P23" t="n">
-        <v>347.8383983481323</v>
+        <v>347.7967973220868</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -36165,28 +36271,28 @@
         <v>0.0843</v>
       </c>
       <c r="I24" t="n">
-        <v>0.06695005623974293</v>
+        <v>0.07140990926365245</v>
       </c>
       <c r="J24" t="n">
+        <v>319</v>
+      </c>
+      <c r="K24" t="n">
         <v>318</v>
       </c>
-      <c r="K24" t="n">
-        <v>317</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.001449458600753295</v>
+        <v>0.001656947294684574</v>
       </c>
       <c r="M24" t="n">
-        <v>9.796110063443248</v>
+        <v>9.787957985499816</v>
       </c>
       <c r="N24" t="n">
-        <v>159.9937238908848</v>
+        <v>159.6601469180166</v>
       </c>
       <c r="O24" t="n">
-        <v>12.64886255324505</v>
+        <v>12.63566962681506</v>
       </c>
       <c r="P24" t="n">
-        <v>346.9963683810135</v>
+        <v>346.9475861666811</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -36243,28 +36349,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.002438149024571652</v>
+        <v>0.001241299433975703</v>
       </c>
       <c r="J25" t="n">
+        <v>319</v>
+      </c>
+      <c r="K25" t="n">
         <v>318</v>
       </c>
-      <c r="K25" t="n">
-        <v>317</v>
-      </c>
       <c r="L25" t="n">
-        <v>1.771034216946354e-06</v>
+        <v>4.615413738973118e-07</v>
       </c>
       <c r="M25" t="n">
-        <v>10.46273903659718</v>
+        <v>10.45132397363701</v>
       </c>
       <c r="N25" t="n">
-        <v>173.9120168649397</v>
+        <v>173.4805266732232</v>
       </c>
       <c r="O25" t="n">
-        <v>13.18757054445358</v>
+        <v>13.17120065420094</v>
       </c>
       <c r="P25" t="n">
-        <v>342.5452968027835</v>
+        <v>342.5050507134242</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -36321,28 +36427,28 @@
         <v>0.0467</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2348382406036078</v>
+        <v>0.2342106532099844</v>
       </c>
       <c r="J26" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K26" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0132770600925245</v>
+        <v>0.01328605808026984</v>
       </c>
       <c r="M26" t="n">
-        <v>11.7547765712281</v>
+        <v>11.72116826303863</v>
       </c>
       <c r="N26" t="n">
-        <v>214.4694616215746</v>
+        <v>213.8005472780842</v>
       </c>
       <c r="O26" t="n">
-        <v>14.64477591571734</v>
+        <v>14.6219200954623</v>
       </c>
       <c r="P26" t="n">
-        <v>338.6419059487899</v>
+        <v>338.6487243061963</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -36399,28 +36505,28 @@
         <v>0.0484</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1319401085122745</v>
+        <v>-0.1269073715667972</v>
       </c>
       <c r="J27" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K27" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L27" t="n">
-        <v>0.003070029745536274</v>
+        <v>0.00285603167844084</v>
       </c>
       <c r="M27" t="n">
-        <v>12.01987287755332</v>
+        <v>12.00619172652692</v>
       </c>
       <c r="N27" t="n">
-        <v>295.8082376817815</v>
+        <v>295.0998229277106</v>
       </c>
       <c r="O27" t="n">
-        <v>17.19907665201192</v>
+        <v>17.17846974930278</v>
       </c>
       <c r="P27" t="n">
-        <v>339.7244561110407</v>
+        <v>339.6697784684121</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -36477,28 +36583,28 @@
         <v>0.0576</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2342371239970477</v>
+        <v>-0.2288521681286566</v>
       </c>
       <c r="J28" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K28" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0205969477304484</v>
+        <v>0.01976071404101143</v>
       </c>
       <c r="M28" t="n">
-        <v>9.300744121525716</v>
+        <v>9.301045641852587</v>
       </c>
       <c r="N28" t="n">
-        <v>136.5226035341176</v>
+        <v>136.3452262859806</v>
       </c>
       <c r="O28" t="n">
-        <v>11.68428874746416</v>
+        <v>11.6766958633845</v>
       </c>
       <c r="P28" t="n">
-        <v>348.8071259187585</v>
+        <v>348.7486216305884</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -36555,28 +36661,28 @@
         <v>0.2</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1812771462893725</v>
+        <v>0.1825568369819811</v>
       </c>
       <c r="J29" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K29" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L29" t="n">
-        <v>0.005818885669904628</v>
+        <v>0.005937841134605937</v>
       </c>
       <c r="M29" t="n">
-        <v>10.15670474396733</v>
+        <v>10.13065665808533</v>
       </c>
       <c r="N29" t="n">
-        <v>289.1168299752541</v>
+        <v>288.1975083557782</v>
       </c>
       <c r="O29" t="n">
-        <v>17.0034358285393</v>
+        <v>16.97638089687488</v>
       </c>
       <c r="P29" t="n">
-        <v>344.0348044467125</v>
+        <v>344.020797169488</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -36614,7 +36720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD319"/>
+  <dimension ref="A1:AD320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84731,7 +84837,7 @@
       </c>
       <c r="P318" t="inlineStr">
         <is>
-          <t>-38.375339234739286,174.659283136492</t>
+          <t>-38.37545995998763,174.65981794907623</t>
         </is>
       </c>
       <c r="Q318" t="inlineStr">
@@ -84883,7 +84989,7 @@
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>-38.375339234739286,174.659283136492</t>
+          <t>-38.37545995998763,174.65981794907623</t>
         </is>
       </c>
       <c r="Q319" t="inlineStr">
@@ -84954,6 +85060,158 @@
       <c r="AD319" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>-38.38455062142876,174.65504343558376</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>-38.38399141349058,174.6556364926408</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>-38.383371309576475,174.6560649273394</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>-38.38274495394515,174.65647647490664</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-38.38213119957282,174.6569221059056</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>-38.38150969905795,174.6573468094775</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>-38.38086953181745,174.6577210611016</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>-38.38021908982559,174.65806754938527</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>-38.379559696362,174.65841893494232</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>-38.37885083273316,174.6585962589366</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>-38.378164344887765,174.65881320715425</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>-38.37748272593239,174.65903988455364</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>-38.3768175418615,174.65933939790202</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>-38.376155877990485,174.65965453369222</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>-38.37542442067957,174.6596605087009</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>-38.374791658222236,174.66009928476544</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>-38.374121120618625,174.66036638937797</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>-38.373463950853214,174.66068787618414</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>-38.372794565236966,174.660969179173</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>-38.37213172239554,174.66127278977987</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>-38.3714782511948,174.6616078834655</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>-38.37082599030143,174.6619483302304</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>-38.370167771812284,174.66226819051894</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>-38.369530631351715,174.66266282470818</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>-38.368885251509,174.66302825929725</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>-38.36822082907476,174.6633322510246</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>-38.3675327225327,174.6635452139429</t>
+        </is>
+      </c>
+      <c r="AC320" t="inlineStr">
+        <is>
+          <t>-38.36686680557665,174.66383874572483</t>
+        </is>
+      </c>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0257/nzd0257.xlsx
+++ b/data/nzd0257/nzd0257.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD320"/>
+  <dimension ref="A1:AD321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31130,6 +31130,102 @@
       <c r="AD320" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:06:21+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>357.92</v>
+      </c>
+      <c r="C321" t="n">
+        <v>339.43</v>
+      </c>
+      <c r="D321" t="n">
+        <v>336.37</v>
+      </c>
+      <c r="E321" t="n">
+        <v>334.18</v>
+      </c>
+      <c r="F321" t="n">
+        <v>329.14</v>
+      </c>
+      <c r="G321" t="n">
+        <v>323.35</v>
+      </c>
+      <c r="H321" t="n">
+        <v>322.05</v>
+      </c>
+      <c r="I321" t="n">
+        <v>332.35</v>
+      </c>
+      <c r="J321" t="n">
+        <v>335.95</v>
+      </c>
+      <c r="K321" t="n">
+        <v>347.48</v>
+      </c>
+      <c r="L321" t="n">
+        <v>355.02</v>
+      </c>
+      <c r="M321" t="n">
+        <v>357.93</v>
+      </c>
+      <c r="N321" t="n">
+        <v>353.77</v>
+      </c>
+      <c r="O321" t="n">
+        <v>350.64</v>
+      </c>
+      <c r="P321" t="n">
+        <v>366</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>360.86</v>
+      </c>
+      <c r="R321" t="n">
+        <v>361.79</v>
+      </c>
+      <c r="S321" t="n">
+        <v>359.1</v>
+      </c>
+      <c r="T321" t="n">
+        <v>357.46</v>
+      </c>
+      <c r="U321" t="n">
+        <v>360.21</v>
+      </c>
+      <c r="V321" t="n">
+        <v>361.43</v>
+      </c>
+      <c r="W321" t="n">
+        <v>359.33</v>
+      </c>
+      <c r="X321" t="n">
+        <v>357.97</v>
+      </c>
+      <c r="Y321" t="n">
+        <v>350.34</v>
+      </c>
+      <c r="Z321" t="n">
+        <v>346.03</v>
+      </c>
+      <c r="AA321" t="n">
+        <v>347.85</v>
+      </c>
+      <c r="AB321" t="n">
+        <v>353.76</v>
+      </c>
+      <c r="AC321" t="n">
+        <v>354.21</v>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -31144,7 +31240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B324"/>
+  <dimension ref="A1:B325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34387,6 +34483,16 @@
       </c>
       <c r="B324" t="n">
         <v>-0.5</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -34555,28 +34661,28 @@
         <v>0.099</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6781330030896769</v>
+        <v>-0.6731245419629919</v>
       </c>
       <c r="J2" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K2" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3981170960948885</v>
+        <v>0.39461931889055</v>
       </c>
       <c r="M2" t="n">
-        <v>4.860063508136913</v>
+        <v>4.875084503058616</v>
       </c>
       <c r="N2" t="n">
-        <v>36.48642779248016</v>
+        <v>36.58780234765256</v>
       </c>
       <c r="O2" t="n">
-        <v>6.040399638474275</v>
+        <v>6.048785196025112</v>
       </c>
       <c r="P2" t="n">
-        <v>367.3732770990044</v>
+        <v>367.3185805360039</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34633,28 +34739,28 @@
         <v>0.1919</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5507446273297031</v>
+        <v>-0.5490287303695111</v>
       </c>
       <c r="J3" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K3" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3398371457107554</v>
+        <v>0.3396242023021426</v>
       </c>
       <c r="M3" t="n">
-        <v>4.426442275341498</v>
+        <v>4.422307514457437</v>
       </c>
       <c r="N3" t="n">
-        <v>30.92296855401377</v>
+        <v>30.85161611801056</v>
       </c>
       <c r="O3" t="n">
-        <v>5.560842432043348</v>
+        <v>5.554423112980372</v>
       </c>
       <c r="P3" t="n">
-        <v>351.0197989585672</v>
+        <v>351.0010599359787</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34711,28 +34817,28 @@
         <v>0.1119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3649653820290573</v>
+        <v>-0.3612175273617799</v>
       </c>
       <c r="J4" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K4" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3116515549886832</v>
+        <v>0.3068796420484354</v>
       </c>
       <c r="M4" t="n">
-        <v>3.031401202443845</v>
+        <v>3.045647302928588</v>
       </c>
       <c r="N4" t="n">
-        <v>15.43983966753335</v>
+        <v>15.51220251448819</v>
       </c>
       <c r="O4" t="n">
-        <v>3.929356139055526</v>
+        <v>3.938553353007699</v>
       </c>
       <c r="P4" t="n">
-        <v>339.7091953032773</v>
+        <v>339.6682656117532</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34789,28 +34895,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1082891891270307</v>
+        <v>-0.102225658349944</v>
       </c>
       <c r="J5" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K5" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03158753593573793</v>
+        <v>0.02795856031573296</v>
       </c>
       <c r="M5" t="n">
-        <v>3.192417995996529</v>
+        <v>3.21444308907442</v>
       </c>
       <c r="N5" t="n">
-        <v>18.86753779965509</v>
+        <v>19.12427883174979</v>
       </c>
       <c r="O5" t="n">
-        <v>4.343677911592328</v>
+        <v>4.373131467466967</v>
       </c>
       <c r="P5" t="n">
-        <v>326.9238079646807</v>
+        <v>326.8575891631835</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34867,28 +34973,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1567019186430925</v>
+        <v>-0.1499803843115352</v>
       </c>
       <c r="J6" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K6" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03715561703251646</v>
+        <v>0.03396291832801157</v>
       </c>
       <c r="M6" t="n">
-        <v>4.665977376939886</v>
+        <v>4.683206082446719</v>
       </c>
       <c r="N6" t="n">
-        <v>33.39493904205742</v>
+        <v>33.67851857327119</v>
       </c>
       <c r="O6" t="n">
-        <v>5.778835439953055</v>
+        <v>5.803319616673821</v>
       </c>
       <c r="P6" t="n">
-        <v>322.0563574791025</v>
+        <v>321.9829527312714</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34945,28 +35051,28 @@
         <v>0.0725</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4030259502599881</v>
+        <v>-0.3973587758172216</v>
       </c>
       <c r="J7" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K7" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L7" t="n">
-        <v>0.126626781955142</v>
+        <v>0.1236810093322789</v>
       </c>
       <c r="M7" t="n">
-        <v>6.304378095795464</v>
+        <v>6.313514699460425</v>
       </c>
       <c r="N7" t="n">
-        <v>58.79504475565667</v>
+        <v>58.88708813002661</v>
       </c>
       <c r="O7" t="n">
-        <v>7.667792691228465</v>
+        <v>7.673792291300737</v>
       </c>
       <c r="P7" t="n">
-        <v>324.4856272720339</v>
+        <v>324.4237370115122</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35023,28 +35129,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4988961852372381</v>
+        <v>-0.4954773183344099</v>
       </c>
       <c r="J8" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K8" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1460464223981331</v>
+        <v>0.1449326431436655</v>
       </c>
       <c r="M8" t="n">
-        <v>6.988122200319373</v>
+        <v>6.984525485297334</v>
       </c>
       <c r="N8" t="n">
-        <v>76.37726624470319</v>
+        <v>76.23895422437604</v>
       </c>
       <c r="O8" t="n">
-        <v>8.739408804072687</v>
+        <v>8.73149209610683</v>
       </c>
       <c r="P8" t="n">
-        <v>329.4493472249248</v>
+        <v>329.4120103535365</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35101,28 +35207,28 @@
         <v>0.0678</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5503545527688757</v>
+        <v>-0.5442441499243709</v>
       </c>
       <c r="J9" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K9" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L9" t="n">
-        <v>0.148222593500772</v>
+        <v>0.1457444506109209</v>
       </c>
       <c r="M9" t="n">
-        <v>7.472755521884565</v>
+        <v>7.480217111151475</v>
       </c>
       <c r="N9" t="n">
-        <v>91.29441580713608</v>
+        <v>91.32792362717096</v>
       </c>
       <c r="O9" t="n">
-        <v>9.554811134037976</v>
+        <v>9.55656442594152</v>
       </c>
       <c r="P9" t="n">
-        <v>336.6468979266749</v>
+        <v>336.5799465603749</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35179,28 +35285,28 @@
         <v>0.0693</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5472417470239738</v>
+        <v>-0.5459051781755124</v>
       </c>
       <c r="J10" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K10" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1592146504415688</v>
+        <v>0.1593517456789751</v>
       </c>
       <c r="M10" t="n">
-        <v>7.293497967046528</v>
+        <v>7.277918970897802</v>
       </c>
       <c r="N10" t="n">
-        <v>82.78392979875942</v>
+        <v>82.53893075379735</v>
       </c>
       <c r="O10" t="n">
-        <v>9.098567458603547</v>
+        <v>9.085093876994192</v>
       </c>
       <c r="P10" t="n">
-        <v>348.095382714101</v>
+        <v>348.0807332559033</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35257,28 +35363,28 @@
         <v>0.076</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4503588198479259</v>
+        <v>-0.4473056368926025</v>
       </c>
       <c r="J11" t="n">
+        <v>320</v>
+      </c>
+      <c r="K11" t="n">
         <v>319</v>
       </c>
-      <c r="K11" t="n">
-        <v>318</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.08194987957769539</v>
+        <v>0.08133882031992878</v>
       </c>
       <c r="M11" t="n">
-        <v>8.772752295720483</v>
+        <v>8.761105647949465</v>
       </c>
       <c r="N11" t="n">
-        <v>118.3271976067803</v>
+        <v>118.0354967064358</v>
       </c>
       <c r="O11" t="n">
-        <v>10.87783055607966</v>
+        <v>10.864414236692</v>
       </c>
       <c r="P11" t="n">
-        <v>354.2464851104984</v>
+        <v>354.2129570051794</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35335,28 +35441,28 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4204323542195237</v>
+        <v>-0.4166606590361189</v>
       </c>
       <c r="J12" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K12" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06776665443285912</v>
+        <v>0.0669580303960039</v>
       </c>
       <c r="M12" t="n">
-        <v>8.925152015660439</v>
+        <v>8.917749165626372</v>
       </c>
       <c r="N12" t="n">
-        <v>127.6148607685332</v>
+        <v>127.3382160117922</v>
       </c>
       <c r="O12" t="n">
-        <v>11.29667476598903</v>
+        <v>11.28442360122094</v>
       </c>
       <c r="P12" t="n">
-        <v>359.7675891943546</v>
+        <v>359.7263991445569</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35413,28 +35519,28 @@
         <v>0.0576</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5753959826312915</v>
+        <v>-0.571198304186264</v>
       </c>
       <c r="J13" t="n">
+        <v>320</v>
+      </c>
+      <c r="K13" t="n">
         <v>319</v>
       </c>
-      <c r="K13" t="n">
-        <v>318</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1027081131998077</v>
+        <v>0.1018345988024383</v>
       </c>
       <c r="M13" t="n">
-        <v>9.671679477137594</v>
+        <v>9.662642851925327</v>
       </c>
       <c r="N13" t="n">
-        <v>150.6301132537527</v>
+        <v>150.307682207457</v>
       </c>
       <c r="O13" t="n">
-        <v>12.27314602103929</v>
+        <v>12.26000335266908</v>
       </c>
       <c r="P13" t="n">
-        <v>366.0841218995394</v>
+        <v>366.0380256756773</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35491,28 +35597,28 @@
         <v>0.067</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5065523780779063</v>
+        <v>-0.5082018673381636</v>
       </c>
       <c r="J14" t="n">
+        <v>320</v>
+      </c>
+      <c r="K14" t="n">
         <v>319</v>
       </c>
-      <c r="K14" t="n">
-        <v>318</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.07655385982160889</v>
+        <v>0.07744113388169538</v>
       </c>
       <c r="M14" t="n">
-        <v>9.845087800543848</v>
+        <v>9.822989129109194</v>
       </c>
       <c r="N14" t="n">
-        <v>161.1915817415823</v>
+        <v>160.7094042635094</v>
       </c>
       <c r="O14" t="n">
-        <v>12.69612467415086</v>
+        <v>12.6771212924508</v>
       </c>
       <c r="P14" t="n">
-        <v>369.7953828859239</v>
+        <v>369.813496523544</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35569,28 +35675,28 @@
         <v>0.074</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.922894221459275</v>
+        <v>-0.9264654017034032</v>
       </c>
       <c r="J15" t="n">
+        <v>320</v>
+      </c>
+      <c r="K15" t="n">
         <v>319</v>
       </c>
-      <c r="K15" t="n">
-        <v>318</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.2176767444055909</v>
+        <v>0.2199276759041087</v>
       </c>
       <c r="M15" t="n">
-        <v>9.596783993932856</v>
+        <v>9.589327767294785</v>
       </c>
       <c r="N15" t="n">
-        <v>159.4142801774277</v>
+        <v>159.0229444954441</v>
       </c>
       <c r="O15" t="n">
-        <v>12.62593680395351</v>
+        <v>12.61042998852315</v>
       </c>
       <c r="P15" t="n">
-        <v>380.7664710178689</v>
+        <v>380.8056874385979</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35647,28 +35753,28 @@
         <v>0.0895</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6444173822702229</v>
+        <v>-0.639762805516919</v>
       </c>
       <c r="J16" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K16" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1333832105717612</v>
+        <v>0.1322737710787288</v>
       </c>
       <c r="M16" t="n">
-        <v>9.036305182660801</v>
+        <v>9.031735147206099</v>
       </c>
       <c r="N16" t="n">
-        <v>138.4249764456862</v>
+        <v>138.1697897252398</v>
       </c>
       <c r="O16" t="n">
-        <v>11.76541441878212</v>
+        <v>11.75456463358979</v>
       </c>
       <c r="P16" t="n">
-        <v>375.3008142455798</v>
+        <v>375.2492181014483</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35725,28 +35831,28 @@
         <v>0.0617</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8587982509205349</v>
+        <v>-0.8555433523875668</v>
       </c>
       <c r="J17" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K17" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1336304355203856</v>
+        <v>0.133426896677906</v>
       </c>
       <c r="M17" t="n">
-        <v>12.19056060449151</v>
+        <v>12.16572055664022</v>
       </c>
       <c r="N17" t="n">
-        <v>247.4252173728084</v>
+        <v>246.7307237667046</v>
       </c>
       <c r="O17" t="n">
-        <v>15.72975579507859</v>
+        <v>15.70766449115541</v>
       </c>
       <c r="P17" t="n">
-        <v>378.0854565123221</v>
+        <v>378.0495664919112</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35803,28 +35909,28 @@
         <v>0.0469</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4277126317243938</v>
+        <v>-0.4295401546346184</v>
       </c>
       <c r="J18" t="n">
+        <v>320</v>
+      </c>
+      <c r="K18" t="n">
         <v>319</v>
       </c>
-      <c r="K18" t="n">
-        <v>318</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.05344000376039937</v>
+        <v>0.05417712395356677</v>
       </c>
       <c r="M18" t="n">
-        <v>10.25874969545751</v>
+        <v>10.23731962959941</v>
       </c>
       <c r="N18" t="n">
-        <v>169.0678040984485</v>
+        <v>168.5662838442049</v>
       </c>
       <c r="O18" t="n">
-        <v>13.00260758842043</v>
+        <v>12.98330789299109</v>
       </c>
       <c r="P18" t="n">
-        <v>376.0447529765296</v>
+        <v>376.0648002879527</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35881,28 +35987,28 @@
         <v>0.0659</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2094941629217727</v>
+        <v>-0.2121866690227604</v>
       </c>
       <c r="J19" t="n">
+        <v>320</v>
+      </c>
+      <c r="K19" t="n">
         <v>319</v>
       </c>
-      <c r="K19" t="n">
-        <v>318</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.01318235425365655</v>
+        <v>0.0135959959642119</v>
       </c>
       <c r="M19" t="n">
-        <v>10.77019340657715</v>
+        <v>10.75080893935449</v>
       </c>
       <c r="N19" t="n">
-        <v>170.7246528433675</v>
+        <v>170.2508656838465</v>
       </c>
       <c r="O19" t="n">
-        <v>13.06616442738141</v>
+        <v>13.0480215237348</v>
       </c>
       <c r="P19" t="n">
-        <v>369.0432757225108</v>
+        <v>369.072878410755</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35959,28 +36065,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.01710288741281895</v>
+        <v>-0.01884290601645668</v>
       </c>
       <c r="J20" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K20" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L20" t="n">
-        <v>7.671390698249514e-05</v>
+        <v>9.367445515939821e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>11.2908996406618</v>
+        <v>11.2646740445842</v>
       </c>
       <c r="N20" t="n">
-        <v>200.0929827257809</v>
+        <v>199.4936898030792</v>
       </c>
       <c r="O20" t="n">
-        <v>14.14542267752296</v>
+        <v>14.12422351150955</v>
       </c>
       <c r="P20" t="n">
-        <v>360.8024410712933</v>
+        <v>360.8214435222994</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36037,28 +36143,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.04041384176740632</v>
+        <v>0.04074202787451762</v>
       </c>
       <c r="J21" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K21" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0004992759965424254</v>
+        <v>0.0005105214034298866</v>
       </c>
       <c r="M21" t="n">
-        <v>10.29609664333681</v>
+        <v>10.26492566956364</v>
       </c>
       <c r="N21" t="n">
-        <v>169.7697098282382</v>
+        <v>169.2333784199938</v>
       </c>
       <c r="O21" t="n">
-        <v>13.02957059262654</v>
+        <v>13.00897299635885</v>
       </c>
       <c r="P21" t="n">
-        <v>358.6074841758596</v>
+        <v>358.6038635992633</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36115,28 +36221,28 @@
         <v>0.0557</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1837534001996571</v>
+        <v>0.1856659990340077</v>
       </c>
       <c r="J22" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K22" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L22" t="n">
-        <v>0.00939365726015795</v>
+        <v>0.009644968486198779</v>
       </c>
       <c r="M22" t="n">
-        <v>10.88057647002874</v>
+        <v>10.85432310361307</v>
       </c>
       <c r="N22" t="n">
-        <v>184.882016464729</v>
+        <v>184.3280063553728</v>
       </c>
       <c r="O22" t="n">
-        <v>13.59713265599512</v>
+        <v>13.57674505746399</v>
       </c>
       <c r="P22" t="n">
-        <v>353.4576196663597</v>
+        <v>353.4365197159722</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36193,28 +36299,28 @@
         <v>0.0982</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1031927069575492</v>
+        <v>0.1085351213695301</v>
       </c>
       <c r="J23" t="n">
+        <v>320</v>
+      </c>
+      <c r="K23" t="n">
         <v>319</v>
       </c>
-      <c r="K23" t="n">
-        <v>318</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.002705760595218987</v>
+        <v>0.003007108603448772</v>
       </c>
       <c r="M23" t="n">
-        <v>11.53931439671782</v>
+        <v>11.52976521663215</v>
       </c>
       <c r="N23" t="n">
-        <v>203.957842416791</v>
+        <v>203.5602052723141</v>
       </c>
       <c r="O23" t="n">
-        <v>14.28138097022802</v>
+        <v>14.2674526553381</v>
       </c>
       <c r="P23" t="n">
-        <v>347.7967973220868</v>
+        <v>347.7380602858918</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -36271,28 +36377,28 @@
         <v>0.0843</v>
       </c>
       <c r="I24" t="n">
-        <v>0.07140990926365245</v>
+        <v>0.07694903948452599</v>
       </c>
       <c r="J24" t="n">
+        <v>320</v>
+      </c>
+      <c r="K24" t="n">
         <v>319</v>
       </c>
-      <c r="K24" t="n">
-        <v>318</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.001656947294684574</v>
+        <v>0.001932121227733008</v>
       </c>
       <c r="M24" t="n">
-        <v>9.787957985499816</v>
+        <v>9.78607070611684</v>
       </c>
       <c r="N24" t="n">
-        <v>159.6601469180166</v>
+        <v>159.4195034322212</v>
       </c>
       <c r="O24" t="n">
-        <v>12.63566962681506</v>
+        <v>12.62614364848671</v>
       </c>
       <c r="P24" t="n">
-        <v>346.9475861666811</v>
+        <v>346.8866863436456</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -36349,28 +36455,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.001241299433975703</v>
+        <v>0.005968197360658471</v>
       </c>
       <c r="J25" t="n">
+        <v>320</v>
+      </c>
+      <c r="K25" t="n">
         <v>319</v>
       </c>
-      <c r="K25" t="n">
-        <v>318</v>
-      </c>
       <c r="L25" t="n">
-        <v>4.615413738973118e-07</v>
+        <v>1.072331085683054e-05</v>
       </c>
       <c r="M25" t="n">
-        <v>10.45132397363701</v>
+        <v>10.44577884919495</v>
       </c>
       <c r="N25" t="n">
-        <v>173.4805266732232</v>
+        <v>173.1259376758655</v>
       </c>
       <c r="O25" t="n">
-        <v>13.17120065420094</v>
+        <v>13.1577329991099</v>
       </c>
       <c r="P25" t="n">
-        <v>342.5050507134242</v>
+        <v>342.4530809572056</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -36427,28 +36533,28 @@
         <v>0.0467</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2342106532099844</v>
+        <v>0.2349502701125142</v>
       </c>
       <c r="J26" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K26" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01328605808026984</v>
+        <v>0.01344953817632211</v>
       </c>
       <c r="M26" t="n">
-        <v>11.72116826303863</v>
+        <v>11.68839947508254</v>
       </c>
       <c r="N26" t="n">
-        <v>213.8005472780842</v>
+        <v>213.1371177774036</v>
       </c>
       <c r="O26" t="n">
-        <v>14.6219200954623</v>
+        <v>14.5992163412083</v>
       </c>
       <c r="P26" t="n">
-        <v>338.6487243061963</v>
+        <v>338.6406470741919</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -36505,28 +36611,28 @@
         <v>0.0484</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1269073715667972</v>
+        <v>-0.1199956124001192</v>
       </c>
       <c r="J27" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K27" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L27" t="n">
-        <v>0.00285603167844084</v>
+        <v>0.002566228003960003</v>
       </c>
       <c r="M27" t="n">
-        <v>12.00619172652692</v>
+        <v>12.00129160872619</v>
       </c>
       <c r="N27" t="n">
-        <v>295.0998229277106</v>
+        <v>294.5878433669077</v>
       </c>
       <c r="O27" t="n">
-        <v>17.17846974930278</v>
+        <v>17.16356150007648</v>
       </c>
       <c r="P27" t="n">
-        <v>339.6697784684121</v>
+        <v>339.594296307097</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -36583,28 +36689,28 @@
         <v>0.0576</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2288521681286566</v>
+        <v>-0.2222357633564604</v>
       </c>
       <c r="J28" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K28" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L28" t="n">
-        <v>0.01976071404101143</v>
+        <v>0.01871704746221758</v>
       </c>
       <c r="M28" t="n">
-        <v>9.301045641852587</v>
+        <v>9.307666237648</v>
       </c>
       <c r="N28" t="n">
-        <v>136.3452262859806</v>
+        <v>136.2950457989282</v>
       </c>
       <c r="O28" t="n">
-        <v>11.6766958633845</v>
+        <v>11.67454692049881</v>
       </c>
       <c r="P28" t="n">
-        <v>348.7486216305884</v>
+        <v>348.6763649850229</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -36661,28 +36767,28 @@
         <v>0.2</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1825568369819811</v>
+        <v>0.1859457074263983</v>
       </c>
       <c r="J29" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K29" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L29" t="n">
-        <v>0.005937841134605937</v>
+        <v>0.006196218275659526</v>
       </c>
       <c r="M29" t="n">
-        <v>10.13065665808533</v>
+        <v>10.11563948902112</v>
       </c>
       <c r="N29" t="n">
-        <v>288.1975083557782</v>
+        <v>287.3636588196065</v>
       </c>
       <c r="O29" t="n">
-        <v>16.97638089687488</v>
+        <v>16.95180399897328</v>
       </c>
       <c r="P29" t="n">
-        <v>344.020797169488</v>
+        <v>343.9835149891802</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -36720,7 +36826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD320"/>
+  <dimension ref="A1:AD321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85215,6 +85321,158 @@
         </is>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:06:21+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>-38.384547747433025,174.65503566552354</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>-38.383985052445006,174.65561929500512</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>-38.3833632242026,174.65604306785332</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-38.38273805651163,174.65645782714213</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-38.382123804041726,174.65690211150005</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>-38.38151241967563,174.65735416487968</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>-38.38088382456113,174.65775970256698</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>-38.380210774775335,174.65804506915015</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>-38.37955520429407,174.65840506885024</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>-38.378851025314376,174.65859702189556</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>-38.37815537917268,174.6587734880568</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>-38.377473636078854,174.6589996156962</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>-38.37680944549403,174.6593035303226</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>-38.37614269044693,174.65959611185085</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>-38.37543000863535,174.65968526346714</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>-38.374767426122794,174.66000002384428</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>-38.37409844163539,174.66028479965084</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>-38.37344925968984,174.6606377908632</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>-38.37279755378762,174.66097936774955</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>-38.37213203684295,174.6612738623165</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>-38.37147151354327,174.66158444743027</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>-38.37081809126476,174.6619203164515</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>-38.37016215137755,174.66224825780486</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>-38.369525254006874,174.6626437540989</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>-38.36887826404897,174.66300347848002</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>-38.36821156704901,174.66329781190376</t>
+        </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>-38.36752694291511,174.66352244988315</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>-38.36685747533404,174.66380168425684</t>
+        </is>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0257/nzd0257.xlsx
+++ b/data/nzd0257/nzd0257.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD321"/>
+  <dimension ref="A1:AD323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31224,6 +31224,198 @@
         <v>354.21</v>
       </c>
       <c r="AD321" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:06:14+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>357.92</v>
+      </c>
+      <c r="C322" t="n">
+        <v>339.43</v>
+      </c>
+      <c r="D322" t="n">
+        <v>336.37</v>
+      </c>
+      <c r="E322" t="n">
+        <v>334.18</v>
+      </c>
+      <c r="F322" t="n">
+        <v>329.14</v>
+      </c>
+      <c r="G322" t="n">
+        <v>323.35</v>
+      </c>
+      <c r="H322" t="n">
+        <v>316.36</v>
+      </c>
+      <c r="I322" t="n">
+        <v>332.35</v>
+      </c>
+      <c r="J322" t="n">
+        <v>346.1</v>
+      </c>
+      <c r="K322" t="n">
+        <v>347.48</v>
+      </c>
+      <c r="L322" t="n">
+        <v>364.15</v>
+      </c>
+      <c r="M322" t="n">
+        <v>357.93</v>
+      </c>
+      <c r="N322" t="n">
+        <v>353.77</v>
+      </c>
+      <c r="O322" t="n">
+        <v>350.64</v>
+      </c>
+      <c r="P322" t="n">
+        <v>366</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>360.86</v>
+      </c>
+      <c r="R322" t="n">
+        <v>361.79</v>
+      </c>
+      <c r="S322" t="n">
+        <v>359.1</v>
+      </c>
+      <c r="T322" t="n">
+        <v>357.46</v>
+      </c>
+      <c r="U322" t="n">
+        <v>360.21</v>
+      </c>
+      <c r="V322" t="n">
+        <v>361.43</v>
+      </c>
+      <c r="W322" t="n">
+        <v>359.33</v>
+      </c>
+      <c r="X322" t="n">
+        <v>357.97</v>
+      </c>
+      <c r="Y322" t="n">
+        <v>350.34</v>
+      </c>
+      <c r="Z322" t="n">
+        <v>346.03</v>
+      </c>
+      <c r="AA322" t="n">
+        <v>347.85</v>
+      </c>
+      <c r="AB322" t="n">
+        <v>353.76</v>
+      </c>
+      <c r="AC322" t="n">
+        <v>354.21</v>
+      </c>
+      <c r="AD322" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>360.01</v>
+      </c>
+      <c r="C323" t="n">
+        <v>342.9</v>
+      </c>
+      <c r="D323" t="n">
+        <v>339.01</v>
+      </c>
+      <c r="E323" t="n">
+        <v>335.43</v>
+      </c>
+      <c r="F323" t="n">
+        <v>330.41</v>
+      </c>
+      <c r="G323" t="n">
+        <v>326.06</v>
+      </c>
+      <c r="H323" t="n">
+        <v>316.36</v>
+      </c>
+      <c r="I323" t="n">
+        <v>337.33</v>
+      </c>
+      <c r="J323" t="n">
+        <v>347.85</v>
+      </c>
+      <c r="K323" t="n">
+        <v>347.48</v>
+      </c>
+      <c r="L323" t="n">
+        <v>367.56</v>
+      </c>
+      <c r="M323" t="n">
+        <v>365.61</v>
+      </c>
+      <c r="N323" t="n">
+        <v>353.77</v>
+      </c>
+      <c r="O323" t="n">
+        <v>350.64</v>
+      </c>
+      <c r="P323" t="n">
+        <v>366</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>360.86</v>
+      </c>
+      <c r="R323" t="n">
+        <v>370.17</v>
+      </c>
+      <c r="S323" t="n">
+        <v>368.29</v>
+      </c>
+      <c r="T323" t="n">
+        <v>366.07</v>
+      </c>
+      <c r="U323" t="n">
+        <v>364.29</v>
+      </c>
+      <c r="V323" t="n">
+        <v>361.9</v>
+      </c>
+      <c r="W323" t="n">
+        <v>364.75</v>
+      </c>
+      <c r="X323" t="n">
+        <v>362.66</v>
+      </c>
+      <c r="Y323" t="n">
+        <v>355.19</v>
+      </c>
+      <c r="Z323" t="n">
+        <v>347.87</v>
+      </c>
+      <c r="AA323" t="n">
+        <v>347.07</v>
+      </c>
+      <c r="AB323" t="n">
+        <v>353.71</v>
+      </c>
+      <c r="AC323" t="n">
+        <v>354.21</v>
+      </c>
+      <c r="AD323" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31240,7 +31432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B325"/>
+  <dimension ref="A1:B327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34493,6 +34685,26 @@
       </c>
       <c r="B325" t="n">
         <v>0.6</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>-0.79</v>
       </c>
     </row>
   </sheetData>
@@ -34661,28 +34873,28 @@
         <v>0.099</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6731245419629919</v>
+        <v>-0.6620242725870825</v>
       </c>
       <c r="J2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L2" t="n">
-        <v>0.39461931889055</v>
+        <v>0.386088552182315</v>
       </c>
       <c r="M2" t="n">
-        <v>4.875084503058616</v>
+        <v>4.910987689314678</v>
       </c>
       <c r="N2" t="n">
-        <v>36.58780234765256</v>
+        <v>36.9007299238866</v>
       </c>
       <c r="O2" t="n">
-        <v>6.048785196025112</v>
+        <v>6.074597099716705</v>
       </c>
       <c r="P2" t="n">
-        <v>367.3185805360039</v>
+        <v>367.1969692857569</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34739,28 +34951,28 @@
         <v>0.1919</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5490287303695111</v>
+        <v>-0.5435610464763309</v>
       </c>
       <c r="J3" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K3" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3396242023021426</v>
+        <v>0.3367851348027572</v>
       </c>
       <c r="M3" t="n">
-        <v>4.422307514457437</v>
+        <v>4.425432719477857</v>
       </c>
       <c r="N3" t="n">
-        <v>30.85161611801056</v>
+        <v>30.80819922117647</v>
       </c>
       <c r="O3" t="n">
-        <v>5.554423112980372</v>
+        <v>5.550513419601511</v>
       </c>
       <c r="P3" t="n">
-        <v>351.0010599359787</v>
+        <v>350.9411411157066</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34817,28 +35029,28 @@
         <v>0.1119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3612175273617799</v>
+        <v>-0.3522849599380473</v>
       </c>
       <c r="J4" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K4" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3068796420484354</v>
+        <v>0.2941091656927175</v>
       </c>
       <c r="M4" t="n">
-        <v>3.045647302928588</v>
+        <v>3.082849205224835</v>
       </c>
       <c r="N4" t="n">
-        <v>15.51220251448819</v>
+        <v>15.77195438300244</v>
       </c>
       <c r="O4" t="n">
-        <v>3.938553353007699</v>
+        <v>3.971391995636095</v>
       </c>
       <c r="P4" t="n">
-        <v>339.6682656117532</v>
+        <v>339.5703966983148</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34895,28 +35107,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.102225658349944</v>
+        <v>-0.08960110409703521</v>
       </c>
       <c r="J5" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K5" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02795856031573296</v>
+        <v>0.02112533667915739</v>
       </c>
       <c r="M5" t="n">
-        <v>3.21444308907442</v>
+        <v>3.262860414551136</v>
       </c>
       <c r="N5" t="n">
-        <v>19.12427883174979</v>
+        <v>19.69783499054994</v>
       </c>
       <c r="O5" t="n">
-        <v>4.373131467466967</v>
+        <v>4.438224306020364</v>
       </c>
       <c r="P5" t="n">
-        <v>326.8575891631835</v>
+        <v>326.7192860431279</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34973,28 +35185,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1499803843115352</v>
+        <v>-0.1360495661505464</v>
       </c>
       <c r="J6" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K6" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03396291832801157</v>
+        <v>0.02777064800770968</v>
       </c>
       <c r="M6" t="n">
-        <v>4.683206082446719</v>
+        <v>4.72119080832613</v>
       </c>
       <c r="N6" t="n">
-        <v>33.67851857327119</v>
+        <v>34.31194689974636</v>
       </c>
       <c r="O6" t="n">
-        <v>5.803319616673821</v>
+        <v>5.857640045252555</v>
       </c>
       <c r="P6" t="n">
-        <v>321.9829527312714</v>
+        <v>321.8303400728819</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35051,28 +35263,28 @@
         <v>0.0725</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3973587758172216</v>
+        <v>-0.3846189041793517</v>
       </c>
       <c r="J7" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K7" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1236810093322789</v>
+        <v>0.1167918534325684</v>
       </c>
       <c r="M7" t="n">
-        <v>6.313514699460425</v>
+        <v>6.34131821268517</v>
       </c>
       <c r="N7" t="n">
-        <v>58.88708813002661</v>
+        <v>59.2352317858423</v>
       </c>
       <c r="O7" t="n">
-        <v>7.673792291300737</v>
+        <v>7.696442800790655</v>
       </c>
       <c r="P7" t="n">
-        <v>324.4237370115122</v>
+        <v>324.2841607509527</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35129,28 +35341,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4954773183344099</v>
+        <v>-0.4954970842491309</v>
       </c>
       <c r="J8" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K8" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1449326431436655</v>
+        <v>0.1464554890475829</v>
       </c>
       <c r="M8" t="n">
-        <v>6.984525485297334</v>
+        <v>6.941242443471715</v>
       </c>
       <c r="N8" t="n">
-        <v>76.23895422437604</v>
+        <v>75.76542277515351</v>
       </c>
       <c r="O8" t="n">
-        <v>8.73149209610683</v>
+        <v>8.704333562953197</v>
       </c>
       <c r="P8" t="n">
-        <v>329.4120103535365</v>
+        <v>329.4122267317646</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35207,28 +35419,28 @@
         <v>0.0678</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5442441499243709</v>
+        <v>-0.5292657519409597</v>
       </c>
       <c r="J9" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K9" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1457444506109209</v>
+        <v>0.139054000171849</v>
       </c>
       <c r="M9" t="n">
-        <v>7.480217111151475</v>
+        <v>7.509890866995383</v>
       </c>
       <c r="N9" t="n">
-        <v>91.32792362717096</v>
+        <v>91.76771095593043</v>
       </c>
       <c r="O9" t="n">
-        <v>9.55656442594152</v>
+        <v>9.579546490097036</v>
       </c>
       <c r="P9" t="n">
-        <v>336.5799465603749</v>
+        <v>336.4152852462789</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35285,28 +35497,28 @@
         <v>0.0693</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5459051781755124</v>
+        <v>-0.5301168768727286</v>
       </c>
       <c r="J10" t="n">
+        <v>322</v>
+      </c>
+      <c r="K10" t="n">
         <v>320</v>
       </c>
-      <c r="K10" t="n">
-        <v>318</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1593517456789751</v>
+        <v>0.1515187052894101</v>
       </c>
       <c r="M10" t="n">
-        <v>7.277918970897802</v>
+        <v>7.319441122998592</v>
       </c>
       <c r="N10" t="n">
-        <v>82.53893075379735</v>
+        <v>83.10607637378851</v>
       </c>
       <c r="O10" t="n">
-        <v>9.085093876994192</v>
+        <v>9.116253417593683</v>
       </c>
       <c r="P10" t="n">
-        <v>348.0807332559033</v>
+        <v>347.9071388972948</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35363,28 +35575,28 @@
         <v>0.076</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4473056368926025</v>
+        <v>-0.4412922232680329</v>
       </c>
       <c r="J11" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K11" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08133882031992878</v>
+        <v>0.0801361776152586</v>
       </c>
       <c r="M11" t="n">
-        <v>8.761105647949465</v>
+        <v>8.737858721688642</v>
       </c>
       <c r="N11" t="n">
-        <v>118.0354967064358</v>
+        <v>117.4550499297462</v>
       </c>
       <c r="O11" t="n">
-        <v>10.864414236692</v>
+        <v>10.83766810387484</v>
       </c>
       <c r="P11" t="n">
-        <v>354.2129570051794</v>
+        <v>354.1467192935872</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35441,28 +35653,28 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4166606590361189</v>
+        <v>-0.3963779949556886</v>
       </c>
       <c r="J12" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K12" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0669580303960039</v>
+        <v>0.06087364728391365</v>
       </c>
       <c r="M12" t="n">
-        <v>8.917749165626372</v>
+        <v>8.973760544928705</v>
       </c>
       <c r="N12" t="n">
-        <v>127.3382160117922</v>
+        <v>128.3459299054146</v>
       </c>
       <c r="O12" t="n">
-        <v>11.28442360122094</v>
+        <v>11.32898626998085</v>
       </c>
       <c r="P12" t="n">
-        <v>359.7263991445569</v>
+        <v>359.5041912733778</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35519,28 +35731,28 @@
         <v>0.0576</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.571198304186264</v>
+        <v>-0.5583390934457539</v>
       </c>
       <c r="J13" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K13" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1018345988024383</v>
+        <v>0.0983494818941838</v>
       </c>
       <c r="M13" t="n">
-        <v>9.662642851925327</v>
+        <v>9.666818645500701</v>
       </c>
       <c r="N13" t="n">
-        <v>150.307682207457</v>
+        <v>150.171135492949</v>
       </c>
       <c r="O13" t="n">
-        <v>12.26000335266908</v>
+        <v>12.25443329954303</v>
       </c>
       <c r="P13" t="n">
-        <v>366.0380256756773</v>
+        <v>365.8963296823335</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35597,28 +35809,28 @@
         <v>0.067</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5082018673381636</v>
+        <v>-0.5113917218997514</v>
       </c>
       <c r="J14" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K14" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L14" t="n">
-        <v>0.07744113388169538</v>
+        <v>0.07920440514688409</v>
       </c>
       <c r="M14" t="n">
-        <v>9.822989129109194</v>
+        <v>9.778522626710002</v>
       </c>
       <c r="N14" t="n">
-        <v>160.7094042635094</v>
+        <v>159.7517093766825</v>
       </c>
       <c r="O14" t="n">
-        <v>12.6771212924508</v>
+        <v>12.6392922814801</v>
       </c>
       <c r="P14" t="n">
-        <v>369.813496523544</v>
+        <v>369.8486325294322</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35675,28 +35887,28 @@
         <v>0.074</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9264654017034032</v>
+        <v>-0.9333851597521065</v>
       </c>
       <c r="J15" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K15" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2199276759041087</v>
+        <v>0.2243807288528824</v>
       </c>
       <c r="M15" t="n">
-        <v>9.589327767294785</v>
+        <v>9.573412400798798</v>
       </c>
       <c r="N15" t="n">
-        <v>159.0229444954441</v>
+        <v>158.2373678351211</v>
       </c>
       <c r="O15" t="n">
-        <v>12.61042998852315</v>
+        <v>12.57924353191086</v>
       </c>
       <c r="P15" t="n">
-        <v>380.8056874385979</v>
+        <v>380.8819081005078</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35753,28 +35965,28 @@
         <v>0.0895</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.639762805516919</v>
+        <v>-0.6305991797303088</v>
       </c>
       <c r="J16" t="n">
+        <v>322</v>
+      </c>
+      <c r="K16" t="n">
         <v>320</v>
       </c>
-      <c r="K16" t="n">
-        <v>318</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1322737710787288</v>
+        <v>0.1300921805318317</v>
       </c>
       <c r="M16" t="n">
-        <v>9.031735147206099</v>
+        <v>9.022141279634974</v>
       </c>
       <c r="N16" t="n">
-        <v>138.1697897252398</v>
+        <v>137.6582621029134</v>
       </c>
       <c r="O16" t="n">
-        <v>11.75456463358979</v>
+        <v>11.73278577759406</v>
       </c>
       <c r="P16" t="n">
-        <v>375.2492181014483</v>
+        <v>375.1473320535037</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35831,28 +36043,28 @@
         <v>0.0617</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8555433523875668</v>
+        <v>-0.849103744482265</v>
       </c>
       <c r="J17" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K17" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L17" t="n">
-        <v>0.133426896677906</v>
+        <v>0.1330221139444987</v>
       </c>
       <c r="M17" t="n">
-        <v>12.16572055664022</v>
+        <v>12.11646172402756</v>
       </c>
       <c r="N17" t="n">
-        <v>246.7307237667046</v>
+        <v>245.3536604072755</v>
       </c>
       <c r="O17" t="n">
-        <v>15.70766449115541</v>
+        <v>15.66376903581241</v>
       </c>
       <c r="P17" t="n">
-        <v>378.0495664919112</v>
+        <v>377.978344007827</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35909,28 +36121,28 @@
         <v>0.0469</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4295401546346184</v>
+        <v>-0.4280802938467218</v>
       </c>
       <c r="J18" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K18" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05417712395356677</v>
+        <v>0.05441613397830791</v>
       </c>
       <c r="M18" t="n">
-        <v>10.23731962959941</v>
+        <v>10.19870628123688</v>
       </c>
       <c r="N18" t="n">
-        <v>168.5662838442049</v>
+        <v>167.6347340983776</v>
       </c>
       <c r="O18" t="n">
-        <v>12.98330789299109</v>
+        <v>12.94738329155268</v>
       </c>
       <c r="P18" t="n">
-        <v>376.0648002879527</v>
+        <v>376.0486801748438</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35987,28 +36199,28 @@
         <v>0.0659</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2121866690227604</v>
+        <v>-0.2119338578872418</v>
       </c>
       <c r="J19" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K19" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0135959959642119</v>
+        <v>0.01371774808755954</v>
       </c>
       <c r="M19" t="n">
-        <v>10.75080893935449</v>
+        <v>10.71242839668498</v>
       </c>
       <c r="N19" t="n">
-        <v>170.2508656838465</v>
+        <v>169.3220345958772</v>
       </c>
       <c r="O19" t="n">
-        <v>13.0480215237348</v>
+        <v>13.01238005116194</v>
       </c>
       <c r="P19" t="n">
-        <v>369.072878410755</v>
+        <v>369.0700281070276</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36065,28 +36277,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.01884290601645668</v>
+        <v>-0.01712719167171035</v>
       </c>
       <c r="J20" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K20" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L20" t="n">
-        <v>9.367445515939821e-05</v>
+        <v>7.828950618382624e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>11.2646740445842</v>
+        <v>11.22145551741765</v>
       </c>
       <c r="N20" t="n">
-        <v>199.4936898030792</v>
+        <v>198.3823745550218</v>
       </c>
       <c r="O20" t="n">
-        <v>14.12422351150955</v>
+        <v>14.08482781417728</v>
       </c>
       <c r="P20" t="n">
-        <v>360.8214435222994</v>
+        <v>360.802590955098</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36143,28 +36355,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.04074202787451762</v>
+        <v>0.04383587916184492</v>
       </c>
       <c r="J21" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K21" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0005105214034298866</v>
+        <v>0.0005979418856759677</v>
       </c>
       <c r="M21" t="n">
-        <v>10.26492566956364</v>
+        <v>10.21347027858126</v>
       </c>
       <c r="N21" t="n">
-        <v>169.2333784199938</v>
+        <v>168.2359846485948</v>
       </c>
       <c r="O21" t="n">
-        <v>13.00897299635885</v>
+        <v>12.9705815077272</v>
       </c>
       <c r="P21" t="n">
-        <v>358.6038635992633</v>
+        <v>358.5695987200414</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36221,28 +36433,28 @@
         <v>0.0557</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1856659990340077</v>
+        <v>0.1896785382794815</v>
       </c>
       <c r="J22" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K22" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L22" t="n">
-        <v>0.009644968486198779</v>
+        <v>0.01018017637248969</v>
       </c>
       <c r="M22" t="n">
-        <v>10.85432310361307</v>
+        <v>10.80298577997722</v>
       </c>
       <c r="N22" t="n">
-        <v>184.3280063553728</v>
+        <v>183.2379493650086</v>
       </c>
       <c r="O22" t="n">
-        <v>13.57674505746399</v>
+        <v>13.53654126300395</v>
       </c>
       <c r="P22" t="n">
-        <v>353.4365197159722</v>
+        <v>353.3921134627196</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36299,28 +36511,28 @@
         <v>0.0982</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1085351213695301</v>
+        <v>0.1222367291075191</v>
       </c>
       <c r="J23" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K23" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L23" t="n">
-        <v>0.003007108603448772</v>
+        <v>0.003841792500037133</v>
       </c>
       <c r="M23" t="n">
-        <v>11.52976521663215</v>
+        <v>11.52730832752167</v>
       </c>
       <c r="N23" t="n">
-        <v>203.5602052723141</v>
+        <v>203.1385039039636</v>
       </c>
       <c r="O23" t="n">
-        <v>14.2674526553381</v>
+        <v>14.25266655415623</v>
       </c>
       <c r="P23" t="n">
-        <v>347.7380602858918</v>
+        <v>347.5869217524826</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -36377,28 +36589,28 @@
         <v>0.0843</v>
       </c>
       <c r="I24" t="n">
-        <v>0.07694903948452599</v>
+        <v>0.09060467822664549</v>
       </c>
       <c r="J24" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K24" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L24" t="n">
-        <v>0.001932121227733008</v>
+        <v>0.00269542402538947</v>
       </c>
       <c r="M24" t="n">
-        <v>9.78607070611684</v>
+        <v>9.795712491166247</v>
       </c>
       <c r="N24" t="n">
-        <v>159.4195034322212</v>
+        <v>159.2562031008777</v>
       </c>
       <c r="O24" t="n">
-        <v>12.62614364848671</v>
+        <v>12.61967523753594</v>
       </c>
       <c r="P24" t="n">
-        <v>346.8866863436456</v>
+        <v>346.7360596477886</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -36455,28 +36667,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.005968197360658471</v>
+        <v>0.01812687887769288</v>
       </c>
       <c r="J25" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K25" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L25" t="n">
-        <v>1.072331085683054e-05</v>
+        <v>9.973977412114365e-05</v>
       </c>
       <c r="M25" t="n">
-        <v>10.44577884919495</v>
+        <v>10.44977831538059</v>
       </c>
       <c r="N25" t="n">
-        <v>173.1259376758655</v>
+        <v>172.714485292367</v>
       </c>
       <c r="O25" t="n">
-        <v>13.1577329991099</v>
+        <v>13.14208831549868</v>
       </c>
       <c r="P25" t="n">
-        <v>342.4530809572056</v>
+        <v>342.3189617493498</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -36533,28 +36745,28 @@
         <v>0.0467</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2349502701125142</v>
+        <v>0.2374787522479014</v>
       </c>
       <c r="J26" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K26" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01344953817632211</v>
+        <v>0.01390010780672035</v>
       </c>
       <c r="M26" t="n">
-        <v>11.68839947508254</v>
+        <v>11.62881332721742</v>
       </c>
       <c r="N26" t="n">
-        <v>213.1371177774036</v>
+        <v>211.8461538642142</v>
       </c>
       <c r="O26" t="n">
-        <v>14.5992163412083</v>
+        <v>14.55493572174794</v>
       </c>
       <c r="P26" t="n">
-        <v>338.6406470741919</v>
+        <v>338.6129366645745</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -36611,28 +36823,28 @@
         <v>0.0484</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1199956124001192</v>
+        <v>-0.1069168800425212</v>
       </c>
       <c r="J27" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K27" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L27" t="n">
-        <v>0.002566228003960003</v>
+        <v>0.002058061642246867</v>
       </c>
       <c r="M27" t="n">
-        <v>12.00129160872619</v>
+        <v>11.98792764431012</v>
       </c>
       <c r="N27" t="n">
-        <v>294.5878433669077</v>
+        <v>293.4997758722707</v>
       </c>
       <c r="O27" t="n">
-        <v>17.16356150007648</v>
+        <v>17.13183515774859</v>
       </c>
       <c r="P27" t="n">
-        <v>339.594296307097</v>
+        <v>339.451031583166</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -36689,28 +36901,28 @@
         <v>0.0576</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2222357633564604</v>
+        <v>-0.2092954736911353</v>
       </c>
       <c r="J28" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K28" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L28" t="n">
-        <v>0.01871704746221758</v>
+        <v>0.01674789377004726</v>
       </c>
       <c r="M28" t="n">
-        <v>9.307666237648</v>
+        <v>9.318876461550392</v>
       </c>
       <c r="N28" t="n">
-        <v>136.2950457989282</v>
+        <v>136.1735264306687</v>
       </c>
       <c r="O28" t="n">
-        <v>11.67454692049881</v>
+        <v>11.6693413023473</v>
       </c>
       <c r="P28" t="n">
-        <v>348.6763649850229</v>
+        <v>348.5346119071443</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -36767,28 +36979,28 @@
         <v>0.2</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1859457074263983</v>
+        <v>0.1925591691977281</v>
       </c>
       <c r="J29" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K29" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L29" t="n">
-        <v>0.006196218275659526</v>
+        <v>0.006721987236868232</v>
       </c>
       <c r="M29" t="n">
-        <v>10.11563948902112</v>
+        <v>10.08485180588818</v>
       </c>
       <c r="N29" t="n">
-        <v>287.3636588196065</v>
+        <v>285.7059028393599</v>
       </c>
       <c r="O29" t="n">
-        <v>16.95180399897328</v>
+        <v>16.90283712396709</v>
       </c>
       <c r="P29" t="n">
-        <v>343.9835149891802</v>
+        <v>343.9105393317766</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -36826,7 +37038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD321"/>
+  <dimension ref="A1:AD323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85473,6 +85685,310 @@
         </is>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:06:14+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>-38.384547747433025,174.65503566552354</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>-38.383985052445006,174.65561929500512</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>-38.3833632242026,174.65604306785332</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-38.38273805651163,174.65645782714213</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-38.382123804041726,174.65690211150005</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>-38.38151241967563,174.65735416487968</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>-38.38090562767567,174.65781864895965</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>-38.380210774775335,174.65804506915015</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>-38.37952039928319,174.658297633155</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>-38.378851025314376,174.65859702189556</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>-38.37813270404822,174.65867303509026</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>-38.377473636078854,174.6589996156962</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>-38.37680944549403,174.6593035303226</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>-38.37614269044693,174.65959611185085</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>-38.37543000863535,174.65968526346714</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>-38.374767426122794,174.66000002384428</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>-38.37409844163539,174.66028479965084</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>-38.37344925968984,174.6606377908632</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>-38.37279755378762,174.66097936774955</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>-38.37213203684295,174.6612738623165</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>-38.37147151354327,174.66158444743027</t>
+        </is>
+      </c>
+      <c r="W322" t="inlineStr">
+        <is>
+          <t>-38.37081809126476,174.6619203164515</t>
+        </is>
+      </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>-38.37016215137755,174.66224825780486</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>-38.369525254006874,174.6626437540989</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>-38.36887826404897,174.66300347848002</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>-38.36821156704901,174.66329781190376</t>
+        </is>
+      </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>-38.36752694291511,174.66352244988315</t>
+        </is>
+      </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>-38.36685747533404,174.66380168425684</t>
+        </is>
+      </c>
+      <c r="AD322" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>-38.38453973856209,174.65501401295893</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>-38.383971755552245,174.65558334574</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>-38.38335310789954,174.65601571760254</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-38.38273326662542,174.65644487730768</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-38.38211893755044,174.65688895456177</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>-38.38150203534366,174.65732609003754</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>-38.38090562767567,174.65781864895965</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>-38.38019169229298,174.65799347858353</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>-38.37951439840903,174.65827910976935</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>-38.378851025314376,174.65859702189556</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>-38.37812423500335,174.65863551652774</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>-38.37745456224206,174.6589151171414</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>-38.37680944549403,174.6593035303226</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>-38.37614269044693,174.65959611185085</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>-38.37543000863535,174.65968526346714</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>-38.374767426122794,174.66000002384428</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>-38.37407330269458,174.66019436030174</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>-38.37342034917807,174.6605392290148</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>-38.37277046804818,174.6608870271013</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>-38.37211920738082,174.66123010283044</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>-38.37147006092969,174.66157939470764</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>-38.37080162478938,174.66186191851597</t>
+        </is>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>-38.370147902800475,174.66219772569428</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>-38.369510519458125,174.66259149848855</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>-38.368872674077096,174.6629836538295</t>
+        </is>
+      </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>-38.368213838867604,174.66330625923447</t>
+        </is>
+      </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>-38.367527081183525,174.66352299447783</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>-38.36685747533404,174.66380168425684</t>
+        </is>
+      </c>
+      <c r="AD323" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0257/nzd0257.xlsx
+++ b/data/nzd0257/nzd0257.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD323"/>
+  <dimension ref="A1:AD325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31266,7 +31266,7 @@
         <v>347.48</v>
       </c>
       <c r="L322" t="n">
-        <v>364.15</v>
+        <v>355.02</v>
       </c>
       <c r="M322" t="n">
         <v>357.93</v>
@@ -31350,7 +31350,7 @@
         <v>326.06</v>
       </c>
       <c r="H323" t="n">
-        <v>316.36</v>
+        <v>322.09</v>
       </c>
       <c r="I323" t="n">
         <v>337.33</v>
@@ -31362,13 +31362,13 @@
         <v>347.48</v>
       </c>
       <c r="L323" t="n">
-        <v>367.56</v>
+        <v>360.21</v>
       </c>
       <c r="M323" t="n">
         <v>365.61</v>
       </c>
       <c r="N323" t="n">
-        <v>353.77</v>
+        <v>364.61</v>
       </c>
       <c r="O323" t="n">
         <v>350.64</v>
@@ -31383,7 +31383,7 @@
         <v>370.17</v>
       </c>
       <c r="S323" t="n">
-        <v>368.29</v>
+        <v>359.1</v>
       </c>
       <c r="T323" t="n">
         <v>366.07</v>
@@ -31413,11 +31413,203 @@
         <v>353.71</v>
       </c>
       <c r="AC323" t="n">
-        <v>354.21</v>
+        <v>333.02</v>
       </c>
       <c r="AD323" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>359.66</v>
+      </c>
+      <c r="C324" t="n">
+        <v>341.59</v>
+      </c>
+      <c r="D324" t="n">
+        <v>337.09</v>
+      </c>
+      <c r="E324" t="n">
+        <v>332.65</v>
+      </c>
+      <c r="F324" t="n">
+        <v>329.55</v>
+      </c>
+      <c r="G324" t="n">
+        <v>326.03</v>
+      </c>
+      <c r="H324" t="n">
+        <v>323.27</v>
+      </c>
+      <c r="I324" t="n">
+        <v>337.38</v>
+      </c>
+      <c r="J324" t="n">
+        <v>347.15</v>
+      </c>
+      <c r="K324" t="n">
+        <v>346.63</v>
+      </c>
+      <c r="L324" t="n">
+        <v>358.61</v>
+      </c>
+      <c r="M324" t="n">
+        <v>365.52</v>
+      </c>
+      <c r="N324" t="n">
+        <v>365.73</v>
+      </c>
+      <c r="O324" t="n">
+        <v>348.95</v>
+      </c>
+      <c r="P324" t="n">
+        <v>355.8</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>362.43</v>
+      </c>
+      <c r="R324" t="n">
+        <v>368.76</v>
+      </c>
+      <c r="S324" t="n">
+        <v>358.38</v>
+      </c>
+      <c r="T324" t="n">
+        <v>364.23</v>
+      </c>
+      <c r="U324" t="n">
+        <v>363.82</v>
+      </c>
+      <c r="V324" t="n">
+        <v>362.03</v>
+      </c>
+      <c r="W324" t="n">
+        <v>364.66</v>
+      </c>
+      <c r="X324" t="n">
+        <v>361.76</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>355.43</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>349.1</v>
+      </c>
+      <c r="AA324" t="n">
+        <v>346.91</v>
+      </c>
+      <c r="AB324" t="n">
+        <v>349.59</v>
+      </c>
+      <c r="AC324" t="n">
+        <v>316.61</v>
+      </c>
+      <c r="AD324" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>359.11</v>
+      </c>
+      <c r="C325" t="n">
+        <v>342.05</v>
+      </c>
+      <c r="D325" t="n">
+        <v>336.13</v>
+      </c>
+      <c r="E325" t="n">
+        <v>333</v>
+      </c>
+      <c r="F325" t="n">
+        <v>330.45</v>
+      </c>
+      <c r="G325" t="n">
+        <v>327.55</v>
+      </c>
+      <c r="H325" t="n">
+        <v>324.79</v>
+      </c>
+      <c r="I325" t="n">
+        <v>339.55</v>
+      </c>
+      <c r="J325" t="n">
+        <v>350.34</v>
+      </c>
+      <c r="K325" t="n">
+        <v>348.76</v>
+      </c>
+      <c r="L325" t="n">
+        <v>360.35</v>
+      </c>
+      <c r="M325" t="n">
+        <v>368.62</v>
+      </c>
+      <c r="N325" t="n">
+        <v>374.12</v>
+      </c>
+      <c r="O325" t="n">
+        <v>361.49</v>
+      </c>
+      <c r="P325" t="n">
+        <v>355.8</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>371.21</v>
+      </c>
+      <c r="R325" t="n">
+        <v>373.66</v>
+      </c>
+      <c r="S325" t="n">
+        <v>365.34</v>
+      </c>
+      <c r="T325" t="n">
+        <v>368.04</v>
+      </c>
+      <c r="U325" t="n">
+        <v>366.34</v>
+      </c>
+      <c r="V325" t="n">
+        <v>364.36</v>
+      </c>
+      <c r="W325" t="n">
+        <v>366.11</v>
+      </c>
+      <c r="X325" t="n">
+        <v>363.19</v>
+      </c>
+      <c r="Y325" t="n">
+        <v>356.1</v>
+      </c>
+      <c r="Z325" t="n">
+        <v>349.87</v>
+      </c>
+      <c r="AA325" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="AB325" t="n">
+        <v>349.68</v>
+      </c>
+      <c r="AC325" t="n">
+        <v>315.11</v>
+      </c>
+      <c r="AD325" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -31432,7 +31624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B327"/>
+  <dimension ref="A1:B329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34705,6 +34897,26 @@
       </c>
       <c r="B327" t="n">
         <v>-0.79</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>
@@ -34873,28 +35085,28 @@
         <v>0.099</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6620242725870825</v>
+        <v>-0.650714604500368</v>
       </c>
       <c r="J2" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K2" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L2" t="n">
-        <v>0.386088552182315</v>
+        <v>0.3771895950196483</v>
       </c>
       <c r="M2" t="n">
-        <v>4.910987689314678</v>
+        <v>4.948931632099395</v>
       </c>
       <c r="N2" t="n">
-        <v>36.9007299238866</v>
+        <v>37.23700414051628</v>
       </c>
       <c r="O2" t="n">
-        <v>6.074597099716705</v>
+        <v>6.102213052697872</v>
       </c>
       <c r="P2" t="n">
-        <v>367.1969692857569</v>
+        <v>367.0726999660499</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34951,28 +35163,28 @@
         <v>0.1919</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5435610464763309</v>
+        <v>-0.5374450664321143</v>
       </c>
       <c r="J3" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K3" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3367851348027572</v>
+        <v>0.3332219380189374</v>
       </c>
       <c r="M3" t="n">
-        <v>4.425432719477857</v>
+        <v>4.431927186425406</v>
       </c>
       <c r="N3" t="n">
-        <v>30.80819922117647</v>
+        <v>30.783170450278</v>
       </c>
       <c r="O3" t="n">
-        <v>5.550513419601511</v>
+        <v>5.548258325842263</v>
       </c>
       <c r="P3" t="n">
-        <v>350.9411411157066</v>
+        <v>350.873934263493</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35029,28 +35241,28 @@
         <v>0.1119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3522849599380473</v>
+        <v>-0.3448627870624041</v>
       </c>
       <c r="J4" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K4" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2941091656927175</v>
+        <v>0.2846445046774967</v>
       </c>
       <c r="M4" t="n">
-        <v>3.082849205224835</v>
+        <v>3.110958263271503</v>
       </c>
       <c r="N4" t="n">
-        <v>15.77195438300244</v>
+        <v>15.91876057373025</v>
       </c>
       <c r="O4" t="n">
-        <v>3.971391995636095</v>
+        <v>3.989832148565933</v>
       </c>
       <c r="P4" t="n">
-        <v>339.5703966983148</v>
+        <v>339.4888467070583</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35107,28 +35319,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08960110409703521</v>
+        <v>-0.07966437439504997</v>
       </c>
       <c r="J5" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K5" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02112533667915739</v>
+        <v>0.01661013555188728</v>
       </c>
       <c r="M5" t="n">
-        <v>3.262860414551136</v>
+        <v>3.299138552688528</v>
       </c>
       <c r="N5" t="n">
-        <v>19.69783499054994</v>
+        <v>20.01143905292499</v>
       </c>
       <c r="O5" t="n">
-        <v>4.438224306020364</v>
+        <v>4.473414697177648</v>
       </c>
       <c r="P5" t="n">
-        <v>326.7192860431279</v>
+        <v>326.6100969694111</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35185,28 +35397,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1360495661505464</v>
+        <v>-0.122261307223607</v>
       </c>
       <c r="J6" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K6" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02777064800770968</v>
+        <v>0.02227825789521687</v>
       </c>
       <c r="M6" t="n">
-        <v>4.72119080832613</v>
+        <v>4.759376363545118</v>
       </c>
       <c r="N6" t="n">
-        <v>34.31194689974636</v>
+        <v>34.9389287606144</v>
       </c>
       <c r="O6" t="n">
-        <v>5.857640045252555</v>
+        <v>5.91091606780323</v>
       </c>
       <c r="P6" t="n">
-        <v>321.8303400728819</v>
+        <v>321.6788259437976</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35263,28 +35475,28 @@
         <v>0.0725</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3846189041793517</v>
+        <v>-0.3697786807009766</v>
       </c>
       <c r="J7" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K7" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1167918534325684</v>
+        <v>0.1084904350132843</v>
       </c>
       <c r="M7" t="n">
-        <v>6.34131821268517</v>
+        <v>6.380781927523763</v>
       </c>
       <c r="N7" t="n">
-        <v>59.2352317858423</v>
+        <v>59.84333154571259</v>
       </c>
       <c r="O7" t="n">
-        <v>7.696442800790655</v>
+        <v>7.73584717698796</v>
       </c>
       <c r="P7" t="n">
-        <v>324.2841607509527</v>
+        <v>324.1210832078677</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35341,28 +35553,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4954970842491309</v>
+        <v>-0.4831378023415028</v>
       </c>
       <c r="J8" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K8" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1464554890475829</v>
+        <v>0.140973476561235</v>
       </c>
       <c r="M8" t="n">
-        <v>6.941242443471715</v>
+        <v>6.964423948717644</v>
       </c>
       <c r="N8" t="n">
-        <v>75.76542277515351</v>
+        <v>75.75454110684996</v>
       </c>
       <c r="O8" t="n">
-        <v>8.704333562953197</v>
+        <v>8.703708468627035</v>
       </c>
       <c r="P8" t="n">
-        <v>329.4122267317646</v>
+        <v>329.2764868125054</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35419,28 +35631,28 @@
         <v>0.0678</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5292657519409597</v>
+        <v>-0.5104241910194295</v>
       </c>
       <c r="J9" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L9" t="n">
-        <v>0.139054000171849</v>
+        <v>0.1300160389860144</v>
       </c>
       <c r="M9" t="n">
-        <v>7.509890866995383</v>
+        <v>7.561222082582897</v>
       </c>
       <c r="N9" t="n">
-        <v>91.76771095593043</v>
+        <v>92.77116073984111</v>
       </c>
       <c r="O9" t="n">
-        <v>9.579546490097036</v>
+        <v>9.631778690347963</v>
       </c>
       <c r="P9" t="n">
-        <v>336.4152852462789</v>
+        <v>336.2075388138793</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35497,28 +35709,28 @@
         <v>0.0693</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5301168768727286</v>
+        <v>-0.5126742377981872</v>
       </c>
       <c r="J10" t="n">
+        <v>324</v>
+      </c>
+      <c r="K10" t="n">
         <v>322</v>
       </c>
-      <c r="K10" t="n">
-        <v>320</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1515187052894101</v>
+        <v>0.1425918486525929</v>
       </c>
       <c r="M10" t="n">
-        <v>7.319441122998592</v>
+        <v>7.369394816500018</v>
       </c>
       <c r="N10" t="n">
-        <v>83.10607637378851</v>
+        <v>83.94453690362455</v>
       </c>
       <c r="O10" t="n">
-        <v>9.116253417593683</v>
+        <v>9.162125130319087</v>
       </c>
       <c r="P10" t="n">
-        <v>347.9071388972948</v>
+        <v>347.7147527497701</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35575,28 +35787,28 @@
         <v>0.076</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4412922232680329</v>
+        <v>-0.4351642952628818</v>
       </c>
       <c r="J11" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K11" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0801361776152586</v>
+        <v>0.07886404269241032</v>
       </c>
       <c r="M11" t="n">
-        <v>8.737858721688642</v>
+        <v>8.715266552563278</v>
       </c>
       <c r="N11" t="n">
-        <v>117.4550499297462</v>
+        <v>116.8985784773906</v>
       </c>
       <c r="O11" t="n">
-        <v>10.83766810387484</v>
+        <v>10.81196459841553</v>
       </c>
       <c r="P11" t="n">
-        <v>354.1467192935872</v>
+        <v>354.0789987695109</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35653,28 +35865,28 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3963779949556886</v>
+        <v>-0.3937386587888626</v>
       </c>
       <c r="J12" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K12" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06087364728391365</v>
+        <v>0.06106088657716691</v>
       </c>
       <c r="M12" t="n">
-        <v>8.973760544928705</v>
+        <v>8.9327266818786</v>
       </c>
       <c r="N12" t="n">
-        <v>128.3459299054146</v>
+        <v>126.9661380315203</v>
       </c>
       <c r="O12" t="n">
-        <v>11.32898626998085</v>
+        <v>11.26792518751879</v>
       </c>
       <c r="P12" t="n">
-        <v>359.5041912733778</v>
+        <v>359.4748358751628</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35731,28 +35943,28 @@
         <v>0.0576</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5583390934457539</v>
+        <v>-0.5395686702099405</v>
       </c>
       <c r="J13" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K13" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0983494818941838</v>
+        <v>0.09259225132102689</v>
       </c>
       <c r="M13" t="n">
-        <v>9.666818645500701</v>
+        <v>9.701496445865352</v>
       </c>
       <c r="N13" t="n">
-        <v>150.171135492949</v>
+        <v>150.7923500856072</v>
       </c>
       <c r="O13" t="n">
-        <v>12.25443329954303</v>
+        <v>12.27975366551004</v>
       </c>
       <c r="P13" t="n">
-        <v>365.8963296823335</v>
+        <v>365.6889186737596</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35809,28 +36021,28 @@
         <v>0.067</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5113917218997514</v>
+        <v>-0.488998309062354</v>
       </c>
       <c r="J14" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K14" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L14" t="n">
-        <v>0.07920440514688409</v>
+        <v>0.07313698704398264</v>
       </c>
       <c r="M14" t="n">
-        <v>9.778522626710002</v>
+        <v>9.814988138988051</v>
       </c>
       <c r="N14" t="n">
-        <v>159.7517093766825</v>
+        <v>160.1589533422165</v>
       </c>
       <c r="O14" t="n">
-        <v>12.6392922814801</v>
+        <v>12.65539226346685</v>
       </c>
       <c r="P14" t="n">
-        <v>369.8486325294322</v>
+        <v>369.6013022468925</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35887,28 +36099,28 @@
         <v>0.074</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9333851597521065</v>
+        <v>-0.9346047710394664</v>
       </c>
       <c r="J15" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K15" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2243807288528824</v>
+        <v>0.2266613445962359</v>
       </c>
       <c r="M15" t="n">
-        <v>9.573412400798798</v>
+        <v>9.554459630447035</v>
       </c>
       <c r="N15" t="n">
-        <v>158.2373678351211</v>
+        <v>157.5093235472803</v>
       </c>
       <c r="O15" t="n">
-        <v>12.57924353191086</v>
+        <v>12.55027185152897</v>
       </c>
       <c r="P15" t="n">
-        <v>380.8819081005078</v>
+        <v>380.8952986328167</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35965,28 +36177,28 @@
         <v>0.0895</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6305991797303088</v>
+        <v>-0.6338522937468996</v>
       </c>
       <c r="J16" t="n">
+        <v>324</v>
+      </c>
+      <c r="K16" t="n">
         <v>322</v>
       </c>
-      <c r="K16" t="n">
-        <v>320</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1300921805318317</v>
+        <v>0.1326128152646969</v>
       </c>
       <c r="M16" t="n">
-        <v>9.022141279634974</v>
+        <v>8.982868237684173</v>
       </c>
       <c r="N16" t="n">
-        <v>137.6582621029134</v>
+        <v>136.8483978448686</v>
       </c>
       <c r="O16" t="n">
-        <v>11.73278577759406</v>
+        <v>11.69822199502423</v>
       </c>
       <c r="P16" t="n">
-        <v>375.1473320535037</v>
+        <v>375.1836111374055</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36043,28 +36255,28 @@
         <v>0.0617</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.849103744482265</v>
+        <v>-0.8356574283132834</v>
       </c>
       <c r="J17" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K17" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1330221139444987</v>
+        <v>0.1303444817686388</v>
       </c>
       <c r="M17" t="n">
-        <v>12.11646172402756</v>
+        <v>12.09682661893852</v>
       </c>
       <c r="N17" t="n">
-        <v>245.3536604072755</v>
+        <v>244.7157834372967</v>
       </c>
       <c r="O17" t="n">
-        <v>15.66376903581241</v>
+        <v>15.64339424285205</v>
       </c>
       <c r="P17" t="n">
-        <v>377.978344007827</v>
+        <v>377.8291135362639</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36121,28 +36333,28 @@
         <v>0.0469</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4280802938467218</v>
+        <v>-0.4204703973339841</v>
       </c>
       <c r="J18" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K18" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05441613397830791</v>
+        <v>0.05311467289042415</v>
       </c>
       <c r="M18" t="n">
-        <v>10.19870628123688</v>
+        <v>10.16973761135448</v>
       </c>
       <c r="N18" t="n">
-        <v>167.6347340983776</v>
+        <v>166.8871217364749</v>
       </c>
       <c r="O18" t="n">
-        <v>12.94738329155268</v>
+        <v>12.91847985393308</v>
       </c>
       <c r="P18" t="n">
-        <v>376.0486801748438</v>
+        <v>375.9646555665885</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36199,28 +36411,28 @@
         <v>0.0659</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2119338578872418</v>
+        <v>-0.2192504605745442</v>
       </c>
       <c r="J19" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K19" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01371774808755954</v>
+        <v>0.01483590414674507</v>
       </c>
       <c r="M19" t="n">
-        <v>10.71242839668498</v>
+        <v>10.66688708994703</v>
       </c>
       <c r="N19" t="n">
-        <v>169.3220345958772</v>
+        <v>168.3491199621523</v>
       </c>
       <c r="O19" t="n">
-        <v>13.01238005116194</v>
+        <v>12.97494200226545</v>
       </c>
       <c r="P19" t="n">
-        <v>369.0700281070276</v>
+        <v>369.1507922743492</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36277,28 +36489,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.01712719167171035</v>
+        <v>-0.01033645946502994</v>
       </c>
       <c r="J20" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K20" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L20" t="n">
-        <v>7.828950618382624e-05</v>
+        <v>2.882827762518136e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>11.22145551741765</v>
+        <v>11.18725404291493</v>
       </c>
       <c r="N20" t="n">
-        <v>198.3823745550218</v>
+        <v>197.3830544230472</v>
       </c>
       <c r="O20" t="n">
-        <v>14.08482781417728</v>
+        <v>14.04930796954239</v>
       </c>
       <c r="P20" t="n">
-        <v>360.802590955098</v>
+        <v>360.7279476383925</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36355,28 +36567,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.04383587916184492</v>
+        <v>0.05019776031579395</v>
       </c>
       <c r="J21" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K21" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0005979418856759677</v>
+        <v>0.0007925408159893399</v>
       </c>
       <c r="M21" t="n">
-        <v>10.21347027858126</v>
+        <v>10.17625504442994</v>
       </c>
       <c r="N21" t="n">
-        <v>168.2359846485948</v>
+        <v>167.3705404218434</v>
       </c>
       <c r="O21" t="n">
-        <v>12.9705815077272</v>
+        <v>12.93717667892973</v>
       </c>
       <c r="P21" t="n">
-        <v>358.5695987200414</v>
+        <v>358.4989629647159</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36433,28 +36645,28 @@
         <v>0.0557</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1896785382794815</v>
+        <v>0.1953797923540061</v>
       </c>
       <c r="J22" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K22" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01018017637248969</v>
+        <v>0.01091488811467956</v>
       </c>
       <c r="M22" t="n">
-        <v>10.80298577997722</v>
+        <v>10.75933991920565</v>
       </c>
       <c r="N22" t="n">
-        <v>183.2379493650086</v>
+        <v>182.2426288468283</v>
       </c>
       <c r="O22" t="n">
-        <v>13.53654126300395</v>
+        <v>13.49972699156647</v>
       </c>
       <c r="P22" t="n">
-        <v>353.3921134627196</v>
+        <v>353.3288121313118</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36511,28 +36723,28 @@
         <v>0.0982</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1222367291075191</v>
+        <v>0.139474473189906</v>
       </c>
       <c r="J23" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K23" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L23" t="n">
-        <v>0.003841792500037133</v>
+        <v>0.005024199433594889</v>
       </c>
       <c r="M23" t="n">
-        <v>11.52730832752167</v>
+        <v>11.5451486536354</v>
       </c>
       <c r="N23" t="n">
-        <v>203.1385039039636</v>
+        <v>203.1750485324013</v>
       </c>
       <c r="O23" t="n">
-        <v>14.25266655415623</v>
+        <v>14.25394852426517</v>
       </c>
       <c r="P23" t="n">
-        <v>347.5869217524826</v>
+        <v>347.3962317968161</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -36589,28 +36801,28 @@
         <v>0.0843</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09060467822664549</v>
+        <v>0.1063972644021223</v>
       </c>
       <c r="J24" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K24" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L24" t="n">
-        <v>0.00269542402538947</v>
+        <v>0.003732510992047855</v>
       </c>
       <c r="M24" t="n">
-        <v>9.795712491166247</v>
+        <v>9.815958595213752</v>
       </c>
       <c r="N24" t="n">
-        <v>159.2562031008777</v>
+        <v>159.3569656056284</v>
       </c>
       <c r="O24" t="n">
-        <v>12.61967523753594</v>
+        <v>12.62366688429429</v>
       </c>
       <c r="P24" t="n">
-        <v>346.7360596477886</v>
+        <v>346.561355818575</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -36667,28 +36879,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01812687887769288</v>
+        <v>0.03346271572311529</v>
       </c>
       <c r="J25" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K25" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L25" t="n">
-        <v>9.973977412114365e-05</v>
+        <v>0.0003418989993673183</v>
       </c>
       <c r="M25" t="n">
-        <v>10.44977831538059</v>
+        <v>10.47113546252377</v>
       </c>
       <c r="N25" t="n">
-        <v>172.714485292367</v>
+        <v>172.6677750190953</v>
       </c>
       <c r="O25" t="n">
-        <v>13.14208831549868</v>
+        <v>13.14031107010391</v>
       </c>
       <c r="P25" t="n">
-        <v>342.3189617493498</v>
+        <v>342.1493155448252</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -36745,28 +36957,28 @@
         <v>0.0467</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2374787522479014</v>
+        <v>0.2428913146902219</v>
       </c>
       <c r="J26" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K26" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01390010780672035</v>
+        <v>0.01469577266948152</v>
       </c>
       <c r="M26" t="n">
-        <v>11.62881332721742</v>
+        <v>11.5845474382658</v>
       </c>
       <c r="N26" t="n">
-        <v>211.8461538642142</v>
+        <v>210.6683828338938</v>
       </c>
       <c r="O26" t="n">
-        <v>14.55493572174794</v>
+        <v>14.51441982422631</v>
       </c>
       <c r="P26" t="n">
-        <v>338.6129366645745</v>
+        <v>338.5534573066037</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -36823,28 +37035,28 @@
         <v>0.0484</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1069168800425212</v>
+        <v>-0.09661336489096709</v>
       </c>
       <c r="J27" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K27" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L27" t="n">
-        <v>0.002058061642246867</v>
+        <v>0.001698627683928366</v>
       </c>
       <c r="M27" t="n">
-        <v>11.98792764431012</v>
+        <v>11.96236655863645</v>
       </c>
       <c r="N27" t="n">
-        <v>293.4997758722707</v>
+        <v>292.1698220354381</v>
       </c>
       <c r="O27" t="n">
-        <v>17.13183515774859</v>
+        <v>17.09297580983013</v>
       </c>
       <c r="P27" t="n">
-        <v>339.451031583166</v>
+        <v>339.3378344487624</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -36901,28 +37113,28 @@
         <v>0.0576</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2092954736911353</v>
+        <v>-0.2015265170512089</v>
       </c>
       <c r="J28" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K28" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L28" t="n">
-        <v>0.01674789377004726</v>
+        <v>0.01570119478082477</v>
       </c>
       <c r="M28" t="n">
-        <v>9.318876461550392</v>
+        <v>9.302905659388662</v>
       </c>
       <c r="N28" t="n">
-        <v>136.1735264306687</v>
+        <v>135.5988868469231</v>
       </c>
       <c r="O28" t="n">
-        <v>11.6693413023473</v>
+        <v>11.64469350592462</v>
       </c>
       <c r="P28" t="n">
-        <v>348.5346119071443</v>
+        <v>348.4492444516011</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -36979,28 +37191,28 @@
         <v>0.2</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1925591691977281</v>
+        <v>0.1390844253259214</v>
       </c>
       <c r="J29" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K29" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L29" t="n">
-        <v>0.006721987236868232</v>
+        <v>0.003471507953408559</v>
       </c>
       <c r="M29" t="n">
-        <v>10.08485180588818</v>
+        <v>10.26983743691503</v>
       </c>
       <c r="N29" t="n">
-        <v>285.7059028393599</v>
+        <v>291.3585477016189</v>
       </c>
       <c r="O29" t="n">
-        <v>16.90283712396709</v>
+        <v>17.06922809331514</v>
       </c>
       <c r="P29" t="n">
-        <v>343.9105393317766</v>
+        <v>344.5021000987339</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -37038,7 +37250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD323"/>
+  <dimension ref="A1:AD325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85743,7 +85955,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>-38.37813270404822,174.65867303509026</t>
+          <t>-38.37815537917268,174.6587734880568</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -85875,7 +86087,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>-38.38090562767567,174.65781864895965</t>
+          <t>-38.3808836712878,174.6577592881812</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -85895,7 +86107,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>-38.37812423500335,174.65863551652774</t>
+          <t>-38.37814248938102,174.658716384994</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -85905,7 +86117,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>-38.37680944549403,174.6593035303226</t>
+          <t>-38.376782523750116,174.65918426517487</t>
         </is>
       </c>
       <c r="O323" t="inlineStr">
@@ -85930,7 +86142,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>-38.37342034917807,174.6605392290148</t>
+          <t>-38.37344925968984,174.6606377908632</t>
         </is>
       </c>
       <c r="T323" t="inlineStr">
@@ -85980,12 +86192,316 @@
       </c>
       <c r="AC323" t="inlineStr">
         <is>
-          <t>-38.36685747533404,174.66380168425684</t>
+          <t>-38.36691562450412,174.6640326645548</t>
         </is>
       </c>
       <c r="AD323" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>-38.38454107976085,174.65501763898618</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>-38.383976775418006,174.65559691736308</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>-38.38336046521152,174.6560356086933</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-38.38274391933032,174.65647367774176</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-38.38212223296989,174.65689786398434</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>-38.38150215029939,174.6573264008291</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>-38.38087914972416,174.65774706380188</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>-38.380191500701685,174.6579929606061</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>-38.379516798759056,174.65828651912327</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>-38.378853363800076,174.65860628639695</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>-38.37814646311558,174.658733989019</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>-38.37745478576394,174.65891610735858</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>-38.376779742160686,174.65917194258137</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>-38.376146887615626,174.65961470561737</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>-38.3754553406348,174.65979748511975</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>-38.37476323620265,174.6599828608941</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>-38.374077532521355,174.6602095774195</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>-38.37345152471003,174.66064551279578</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>-38.37277625641223,174.66090676075342</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>-38.37212068528541,174.66123514375087</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>-38.371469659142925,174.66157799714608</t>
+        </is>
+      </c>
+      <c r="W324" t="inlineStr">
+        <is>
+          <t>-38.37080189821818,174.66186288822317</t>
+        </is>
+      </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>-38.37015063707073,174.6622074226863</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>-38.369509790325196,174.66258891264445</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>-38.3688689373005,174.66297040148328</t>
+        </is>
+      </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>-38.36821430488159,174.66330799202035</t>
+        </is>
+      </c>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>-38.36753847449216,174.66356786908716</t>
+        </is>
+      </c>
+      <c r="AC324" t="inlineStr">
+        <is>
+          <t>-38.36696065617575,174.66421154099916</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>-38.384543187358695,174.65502333702923</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>-38.38397501271724,174.65559215175477</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>-38.3833641438662,174.6560455542401</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-38.38274257816284,174.65647005178738</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-38.3821187842751,174.65688854017003</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-38.38149632587403,174.6573106540576</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>-38.38087332533515,174.6577313171459</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>-38.38018318563669,174.65797048038766</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>-38.3795058600172,174.65825275364293</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>-38.37884750382862,174.65858307064744</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>-38.37814214167912,174.6587148446419</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>-38.37744708667192,174.6588819998808</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>-38.37675890503359,174.65907963318205</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>-38.37611574405583,174.65947673771817</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>-38.3754553406348,174.65979748511975</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>-38.37473980462742,174.65988687958978</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>-38.37406283311467,174.66015669524455</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>-38.37342962949305,174.66057086746713</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>-38.37276427071988,174.66086589922713</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>-38.372112761198686,174.6612081158394</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>-38.37146245788478,174.6615529485455</t>
+        </is>
+      </c>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>-38.370797492975406,174.66184726516346</t>
+        </is>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>-38.37014629261871,174.6621920152438</t>
+        </is>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>-38.3695077548288,174.6625816938299</t>
+        </is>
+      </c>
+      <c r="Z325" t="inlineStr">
+        <is>
+          <t>-38.3688665980168,174.66296210529973</t>
+        </is>
+      </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>-38.36822298438744,174.66334026516083</t>
+        </is>
+      </c>
+      <c r="AB325" t="inlineStr">
+        <is>
+          <t>-38.367538225609394,174.66356688881643</t>
+        </is>
+      </c>
+      <c r="AC325" t="inlineStr">
+        <is>
+          <t>-38.36696477240242,174.66422789169025</t>
+        </is>
+      </c>
+      <c r="AD325" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0257/nzd0257.xlsx
+++ b/data/nzd0257/nzd0257.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD325"/>
+  <dimension ref="A1:AD326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31610,6 +31610,102 @@
       <c r="AD325" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:42+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>358.9</v>
+      </c>
+      <c r="C326" t="n">
+        <v>341.87</v>
+      </c>
+      <c r="D326" t="n">
+        <v>335.15</v>
+      </c>
+      <c r="E326" t="n">
+        <v>332.58</v>
+      </c>
+      <c r="F326" t="n">
+        <v>328.61</v>
+      </c>
+      <c r="G326" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="H326" t="n">
+        <v>323.48</v>
+      </c>
+      <c r="I326" t="n">
+        <v>338.75</v>
+      </c>
+      <c r="J326" t="n">
+        <v>347.95</v>
+      </c>
+      <c r="K326" t="n">
+        <v>347.73</v>
+      </c>
+      <c r="L326" t="n">
+        <v>358.85</v>
+      </c>
+      <c r="M326" t="n">
+        <v>365.01</v>
+      </c>
+      <c r="N326" t="n">
+        <v>370.79</v>
+      </c>
+      <c r="O326" t="n">
+        <v>360.63</v>
+      </c>
+      <c r="P326" t="n">
+        <v>339.41</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>371.21</v>
+      </c>
+      <c r="R326" t="n">
+        <v>371.93</v>
+      </c>
+      <c r="S326" t="n">
+        <v>366.03</v>
+      </c>
+      <c r="T326" t="n">
+        <v>365.69</v>
+      </c>
+      <c r="U326" t="n">
+        <v>364.66</v>
+      </c>
+      <c r="V326" t="n">
+        <v>362.78</v>
+      </c>
+      <c r="W326" t="n">
+        <v>367.66</v>
+      </c>
+      <c r="X326" t="n">
+        <v>366.2</v>
+      </c>
+      <c r="Y326" t="n">
+        <v>354.75</v>
+      </c>
+      <c r="Z326" t="n">
+        <v>349.87</v>
+      </c>
+      <c r="AA326" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="AB326" t="n">
+        <v>349.68</v>
+      </c>
+      <c r="AC326" t="n">
+        <v>315.11</v>
+      </c>
+      <c r="AD326" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -31624,7 +31720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B329"/>
+  <dimension ref="A1:B330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34917,6 +35013,16 @@
       </c>
       <c r="B329" t="n">
         <v>1.63</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>-0.77</v>
       </c>
     </row>
   </sheetData>
@@ -35085,28 +35191,28 @@
         <v>0.099</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.650714604500368</v>
+        <v>-0.6454104553429684</v>
       </c>
       <c r="J2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3771895950196483</v>
+        <v>0.3731879496339792</v>
       </c>
       <c r="M2" t="n">
-        <v>4.948931632099395</v>
+        <v>4.966117339452373</v>
       </c>
       <c r="N2" t="n">
-        <v>37.23700414051628</v>
+        <v>37.37207922382376</v>
       </c>
       <c r="O2" t="n">
-        <v>6.102213052697872</v>
+        <v>6.113270746811707</v>
       </c>
       <c r="P2" t="n">
-        <v>367.0726999660499</v>
+        <v>367.0141773569816</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35163,28 +35269,28 @@
         <v>0.1919</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5374450664321143</v>
+        <v>-0.5343896571475019</v>
       </c>
       <c r="J3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3332219380189374</v>
+        <v>0.3314253846478868</v>
       </c>
       <c r="M3" t="n">
-        <v>4.431927186425406</v>
+        <v>4.435120059587786</v>
       </c>
       <c r="N3" t="n">
-        <v>30.783170450278</v>
+        <v>30.77129293554096</v>
       </c>
       <c r="O3" t="n">
-        <v>5.548258325842263</v>
+        <v>5.547187840297187</v>
       </c>
       <c r="P3" t="n">
-        <v>350.873934263493</v>
+        <v>350.8402228202811</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35241,28 +35347,28 @@
         <v>0.1119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3448627870624041</v>
+        <v>-0.3420581880274826</v>
       </c>
       <c r="J4" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K4" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2846445046774967</v>
+        <v>0.2816570130517622</v>
       </c>
       <c r="M4" t="n">
-        <v>3.110958263271503</v>
+        <v>3.119213826062209</v>
       </c>
       <c r="N4" t="n">
-        <v>15.91876057373025</v>
+        <v>15.9395776967436</v>
       </c>
       <c r="O4" t="n">
-        <v>3.989832148565933</v>
+        <v>3.99244006802151</v>
       </c>
       <c r="P4" t="n">
-        <v>339.4888467070583</v>
+        <v>339.4579025446595</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35319,28 +35425,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07966437439504997</v>
+        <v>-0.07492933368374681</v>
       </c>
       <c r="J5" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K5" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01661013555188728</v>
+        <v>0.01466571751018653</v>
       </c>
       <c r="M5" t="n">
-        <v>3.299138552688528</v>
+        <v>3.315778650366274</v>
       </c>
       <c r="N5" t="n">
-        <v>20.01143905292499</v>
+        <v>20.14881742881064</v>
       </c>
       <c r="O5" t="n">
-        <v>4.473414697177648</v>
+        <v>4.488743413118046</v>
       </c>
       <c r="P5" t="n">
-        <v>326.6100969694111</v>
+        <v>326.5578535410596</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35397,28 +35503,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.122261307223607</v>
+        <v>-0.1163021191175902</v>
       </c>
       <c r="J6" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K6" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02227825789521687</v>
+        <v>0.02014285100053803</v>
       </c>
       <c r="M6" t="n">
-        <v>4.759376363545118</v>
+        <v>4.773825492606385</v>
       </c>
       <c r="N6" t="n">
-        <v>34.9389287606144</v>
+        <v>35.14654376294001</v>
       </c>
       <c r="O6" t="n">
-        <v>5.91091606780323</v>
+        <v>5.928452054536666</v>
       </c>
       <c r="P6" t="n">
-        <v>321.6788259437976</v>
+        <v>321.613076051488</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35475,28 +35581,28 @@
         <v>0.0725</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3697786807009766</v>
+        <v>-0.3633532089080941</v>
       </c>
       <c r="J7" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K7" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1084904350132843</v>
+        <v>0.1051344627911613</v>
       </c>
       <c r="M7" t="n">
-        <v>6.380781927523763</v>
+        <v>6.395317978960123</v>
       </c>
       <c r="N7" t="n">
-        <v>59.84333154571259</v>
+        <v>60.02556070004513</v>
       </c>
       <c r="O7" t="n">
-        <v>7.73584717698796</v>
+        <v>7.74761645282245</v>
       </c>
       <c r="P7" t="n">
-        <v>324.1210832078677</v>
+        <v>324.0501886378518</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35553,28 +35659,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4831378023415028</v>
+        <v>-0.4790436235990172</v>
       </c>
       <c r="J8" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K8" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L8" t="n">
-        <v>0.140973476561235</v>
+        <v>0.1394081212779413</v>
       </c>
       <c r="M8" t="n">
-        <v>6.964423948717644</v>
+        <v>6.964822811545561</v>
       </c>
       <c r="N8" t="n">
-        <v>75.75454110684996</v>
+        <v>75.67019253008405</v>
       </c>
       <c r="O8" t="n">
-        <v>8.703708468627035</v>
+        <v>8.698861565175299</v>
       </c>
       <c r="P8" t="n">
-        <v>329.2764868125054</v>
+        <v>329.2313142476148</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35631,28 +35737,28 @@
         <v>0.0678</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5104241910194295</v>
+        <v>-0.5009874611804721</v>
       </c>
       <c r="J9" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K9" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1300160389860144</v>
+        <v>0.1255724641972914</v>
       </c>
       <c r="M9" t="n">
-        <v>7.561222082582897</v>
+        <v>7.586929642177376</v>
       </c>
       <c r="N9" t="n">
-        <v>92.77116073984111</v>
+        <v>93.27520778107781</v>
       </c>
       <c r="O9" t="n">
-        <v>9.631778690347963</v>
+        <v>9.657909079147402</v>
       </c>
       <c r="P9" t="n">
-        <v>336.2075388138793</v>
+        <v>336.1030655047521</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35709,28 +35815,28 @@
         <v>0.0693</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5126742377981872</v>
+        <v>-0.5045532888687313</v>
       </c>
       <c r="J10" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K10" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1425918486525929</v>
+        <v>0.1386160116848412</v>
       </c>
       <c r="M10" t="n">
-        <v>7.369394816500018</v>
+        <v>7.390887340356855</v>
       </c>
       <c r="N10" t="n">
-        <v>83.94453690362455</v>
+        <v>84.26927461683185</v>
       </c>
       <c r="O10" t="n">
-        <v>9.162125130319087</v>
+        <v>9.179829770580271</v>
       </c>
       <c r="P10" t="n">
-        <v>347.7147527497701</v>
+        <v>347.6248218917082</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35787,28 +35893,28 @@
         <v>0.076</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4351642952628818</v>
+        <v>-0.4321158699646812</v>
       </c>
       <c r="J11" t="n">
+        <v>325</v>
+      </c>
+      <c r="K11" t="n">
         <v>324</v>
       </c>
-      <c r="K11" t="n">
-        <v>323</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.07886404269241032</v>
+        <v>0.07823122062050303</v>
       </c>
       <c r="M11" t="n">
-        <v>8.715266552563278</v>
+        <v>8.703879017198668</v>
       </c>
       <c r="N11" t="n">
-        <v>116.8985784773906</v>
+        <v>116.619405286314</v>
       </c>
       <c r="O11" t="n">
-        <v>10.81196459841553</v>
+        <v>10.79904649894212</v>
       </c>
       <c r="P11" t="n">
-        <v>354.0789987695109</v>
+        <v>354.0451796544032</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35865,28 +35971,28 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3937386587888626</v>
+        <v>-0.3879968752181795</v>
       </c>
       <c r="J12" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K12" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06106088657716691</v>
+        <v>0.05960467191299679</v>
       </c>
       <c r="M12" t="n">
-        <v>8.9327266818786</v>
+        <v>8.937111127445803</v>
       </c>
       <c r="N12" t="n">
-        <v>126.9661380315203</v>
+        <v>126.8680192757839</v>
       </c>
       <c r="O12" t="n">
-        <v>11.26792518751879</v>
+        <v>11.26357044971903</v>
       </c>
       <c r="P12" t="n">
-        <v>359.4748358751628</v>
+        <v>359.4114846862557</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35943,28 +36049,28 @@
         <v>0.0576</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5395686702099405</v>
+        <v>-0.5315451132814291</v>
       </c>
       <c r="J13" t="n">
+        <v>325</v>
+      </c>
+      <c r="K13" t="n">
         <v>324</v>
       </c>
-      <c r="K13" t="n">
-        <v>323</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.09259225132102689</v>
+        <v>0.09029088756243808</v>
       </c>
       <c r="M13" t="n">
-        <v>9.701496445865352</v>
+        <v>9.712437417912588</v>
       </c>
       <c r="N13" t="n">
-        <v>150.7923500856072</v>
+        <v>150.8924061367284</v>
       </c>
       <c r="O13" t="n">
-        <v>12.27975366551004</v>
+        <v>12.28382701509299</v>
       </c>
       <c r="P13" t="n">
-        <v>365.6889186737596</v>
+        <v>365.5999056362745</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36021,28 +36127,28 @@
         <v>0.067</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.488998309062354</v>
+        <v>-0.4806639318491535</v>
       </c>
       <c r="J14" t="n">
+        <v>325</v>
+      </c>
+      <c r="K14" t="n">
         <v>324</v>
       </c>
-      <c r="K14" t="n">
-        <v>323</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.07313698704398264</v>
+        <v>0.07098539135646287</v>
       </c>
       <c r="M14" t="n">
-        <v>9.814988138988051</v>
+        <v>9.82676338475258</v>
       </c>
       <c r="N14" t="n">
-        <v>160.1589533422165</v>
+        <v>160.2747591562502</v>
       </c>
       <c r="O14" t="n">
-        <v>12.65539226346685</v>
+        <v>12.65996679127754</v>
       </c>
       <c r="P14" t="n">
-        <v>369.6013022468925</v>
+        <v>369.5088409809098</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36099,28 +36205,28 @@
         <v>0.074</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9346047710394664</v>
+        <v>-0.9319702263533987</v>
       </c>
       <c r="J15" t="n">
+        <v>325</v>
+      </c>
+      <c r="K15" t="n">
         <v>324</v>
       </c>
-      <c r="K15" t="n">
-        <v>323</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.2266613445962359</v>
+        <v>0.2266583064083286</v>
       </c>
       <c r="M15" t="n">
-        <v>9.554459630447035</v>
+        <v>9.535695089877024</v>
       </c>
       <c r="N15" t="n">
-        <v>157.5093235472803</v>
+        <v>157.0841489487881</v>
       </c>
       <c r="O15" t="n">
-        <v>12.55027185152897</v>
+        <v>12.53332154493724</v>
       </c>
       <c r="P15" t="n">
-        <v>380.8952986328167</v>
+        <v>380.8660710935862</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36177,28 +36283,28 @@
         <v>0.0895</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6338522937468996</v>
+        <v>-0.6452030810413942</v>
       </c>
       <c r="J16" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K16" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1326128152646969</v>
+        <v>0.13651087566375</v>
       </c>
       <c r="M16" t="n">
-        <v>8.982868237684173</v>
+        <v>9.013243664064484</v>
       </c>
       <c r="N16" t="n">
-        <v>136.8483978448686</v>
+        <v>137.5319149446225</v>
       </c>
       <c r="O16" t="n">
-        <v>11.69822199502423</v>
+        <v>11.7274001784122</v>
       </c>
       <c r="P16" t="n">
-        <v>375.1836111374055</v>
+        <v>375.3107080073046</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36255,28 +36361,28 @@
         <v>0.0617</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8356574283132834</v>
+        <v>-0.826397332230092</v>
       </c>
       <c r="J17" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K17" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1303444817686388</v>
+        <v>0.1281791892507206</v>
       </c>
       <c r="M17" t="n">
-        <v>12.09682661893852</v>
+        <v>12.09731298973556</v>
       </c>
       <c r="N17" t="n">
-        <v>244.7157834372967</v>
+        <v>244.6941759704908</v>
       </c>
       <c r="O17" t="n">
-        <v>15.64339424285205</v>
+        <v>15.64270360169529</v>
       </c>
       <c r="P17" t="n">
-        <v>377.8291135362639</v>
+        <v>377.7259660471799</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36333,28 +36439,28 @@
         <v>0.0469</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4204703973339841</v>
+        <v>-0.4162904739393103</v>
       </c>
       <c r="J18" t="n">
+        <v>325</v>
+      </c>
+      <c r="K18" t="n">
         <v>324</v>
       </c>
-      <c r="K18" t="n">
-        <v>323</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.05311467289042415</v>
+        <v>0.05237044409456793</v>
       </c>
       <c r="M18" t="n">
-        <v>10.16973761135448</v>
+        <v>10.15691555389764</v>
       </c>
       <c r="N18" t="n">
-        <v>166.8871217364749</v>
+        <v>166.5259608346351</v>
       </c>
       <c r="O18" t="n">
-        <v>12.91847985393308</v>
+        <v>12.90449382326308</v>
       </c>
       <c r="P18" t="n">
-        <v>375.9646555665885</v>
+        <v>375.9183320207111</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36411,28 +36517,28 @@
         <v>0.0659</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2192504605745442</v>
+        <v>-0.2176644511614652</v>
       </c>
       <c r="J19" t="n">
+        <v>325</v>
+      </c>
+      <c r="K19" t="n">
         <v>324</v>
       </c>
-      <c r="K19" t="n">
-        <v>323</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.01483590414674507</v>
+        <v>0.01471034528772464</v>
       </c>
       <c r="M19" t="n">
-        <v>10.66688708994703</v>
+        <v>10.64206694167347</v>
       </c>
       <c r="N19" t="n">
-        <v>168.3491199621523</v>
+        <v>167.8515418764325</v>
       </c>
       <c r="O19" t="n">
-        <v>12.97494200226545</v>
+        <v>12.95575323462255</v>
       </c>
       <c r="P19" t="n">
-        <v>369.1507922743492</v>
+        <v>369.1331765912909</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36489,28 +36595,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.01033645946502994</v>
+        <v>-0.007269657007791379</v>
       </c>
       <c r="J20" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K20" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L20" t="n">
-        <v>2.882827762518136e-05</v>
+        <v>1.433941661466154e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>11.18725404291493</v>
+        <v>11.16849696246229</v>
       </c>
       <c r="N20" t="n">
-        <v>197.3830544230472</v>
+        <v>196.8591808284304</v>
       </c>
       <c r="O20" t="n">
-        <v>14.04930796954239</v>
+        <v>14.03065147555274</v>
       </c>
       <c r="P20" t="n">
-        <v>360.7279476383925</v>
+        <v>360.6941104901584</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36567,28 +36673,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05019776031579395</v>
+        <v>0.05306395603712119</v>
       </c>
       <c r="J21" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K21" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0007925408159893399</v>
+        <v>0.0008904920804242433</v>
       </c>
       <c r="M21" t="n">
-        <v>10.17625504442994</v>
+        <v>10.15639868273884</v>
       </c>
       <c r="N21" t="n">
-        <v>167.3705404218434</v>
+        <v>166.9212008748657</v>
       </c>
       <c r="O21" t="n">
-        <v>12.93717667892973</v>
+        <v>12.91979879390023</v>
       </c>
       <c r="P21" t="n">
-        <v>358.4989629647159</v>
+        <v>358.4670164337988</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36645,28 +36751,28 @@
         <v>0.0557</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1953797923540061</v>
+        <v>0.1979191131058211</v>
       </c>
       <c r="J22" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K22" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01091488811467956</v>
+        <v>0.01126046897101518</v>
       </c>
       <c r="M22" t="n">
-        <v>10.75933991920565</v>
+        <v>10.73641937829053</v>
       </c>
       <c r="N22" t="n">
-        <v>182.2426288468283</v>
+        <v>181.7314590249114</v>
       </c>
       <c r="O22" t="n">
-        <v>13.49972699156647</v>
+        <v>13.48078109847168</v>
       </c>
       <c r="P22" t="n">
-        <v>353.3288121313118</v>
+        <v>353.3005089389295</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36723,28 +36829,28 @@
         <v>0.0982</v>
       </c>
       <c r="I23" t="n">
-        <v>0.139474473189906</v>
+        <v>0.1492724605410223</v>
       </c>
       <c r="J23" t="n">
+        <v>325</v>
+      </c>
+      <c r="K23" t="n">
         <v>324</v>
       </c>
-      <c r="K23" t="n">
-        <v>323</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.005024199433594889</v>
+        <v>0.005761470292498072</v>
       </c>
       <c r="M23" t="n">
-        <v>11.5451486536354</v>
+        <v>11.55995934769383</v>
       </c>
       <c r="N23" t="n">
-        <v>203.1750485324013</v>
+        <v>203.3882747480476</v>
       </c>
       <c r="O23" t="n">
-        <v>14.25394852426517</v>
+        <v>14.26142611200043</v>
       </c>
       <c r="P23" t="n">
-        <v>347.3962317968161</v>
+        <v>347.2874063142157</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -36801,28 +36907,28 @@
         <v>0.0843</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1063972644021223</v>
+        <v>0.1163410887465244</v>
       </c>
       <c r="J24" t="n">
+        <v>325</v>
+      </c>
+      <c r="K24" t="n">
         <v>324</v>
       </c>
-      <c r="K24" t="n">
-        <v>323</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.003732510992047855</v>
+        <v>0.004462159305647195</v>
       </c>
       <c r="M24" t="n">
-        <v>9.815958595213752</v>
+        <v>9.836714571697769</v>
       </c>
       <c r="N24" t="n">
-        <v>159.3569656056284</v>
+        <v>159.7306339665092</v>
       </c>
       <c r="O24" t="n">
-        <v>12.62366688429429</v>
+        <v>12.63845852810022</v>
       </c>
       <c r="P24" t="n">
-        <v>346.561355818575</v>
+        <v>346.4509105358456</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -36879,28 +36985,28 @@
         <v>0.06660000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.03346271572311529</v>
+        <v>0.04038967223821376</v>
       </c>
       <c r="J25" t="n">
+        <v>325</v>
+      </c>
+      <c r="K25" t="n">
         <v>324</v>
       </c>
-      <c r="K25" t="n">
-        <v>323</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.0003418989993673183</v>
+        <v>0.0004998107953700925</v>
       </c>
       <c r="M25" t="n">
-        <v>10.47113546252377</v>
+        <v>10.47760240347335</v>
       </c>
       <c r="N25" t="n">
-        <v>172.6677750190953</v>
+        <v>172.5548510055466</v>
       </c>
       <c r="O25" t="n">
-        <v>13.14031107010391</v>
+        <v>13.13601351268895</v>
       </c>
       <c r="P25" t="n">
-        <v>342.1493155448252</v>
+        <v>342.0723783781711</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -36957,28 +37063,28 @@
         <v>0.0467</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2428913146902219</v>
+        <v>0.24576026540917</v>
       </c>
       <c r="J26" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K26" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01469577266948152</v>
+        <v>0.01512371691209302</v>
       </c>
       <c r="M26" t="n">
-        <v>11.5845474382658</v>
+        <v>11.56331283147489</v>
       </c>
       <c r="N26" t="n">
-        <v>210.6683828338938</v>
+        <v>210.0932101315498</v>
       </c>
       <c r="O26" t="n">
-        <v>14.51441982422631</v>
+        <v>14.49459244447907</v>
       </c>
       <c r="P26" t="n">
-        <v>338.5534573066037</v>
+        <v>338.5218031286424</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -37035,28 +37141,28 @@
         <v>0.0484</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.09661336489096709</v>
+        <v>-0.09242389903370048</v>
       </c>
       <c r="J27" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K27" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L27" t="n">
-        <v>0.001698627683928366</v>
+        <v>0.001563239464677513</v>
       </c>
       <c r="M27" t="n">
-        <v>11.96236655863645</v>
+        <v>11.94505498992777</v>
       </c>
       <c r="N27" t="n">
-        <v>292.1698220354381</v>
+        <v>291.4265844550728</v>
       </c>
       <c r="O27" t="n">
-        <v>17.09297580983013</v>
+        <v>17.07122094213161</v>
       </c>
       <c r="P27" t="n">
-        <v>339.3378344487624</v>
+        <v>339.2916105464372</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -37113,28 +37219,28 @@
         <v>0.0576</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2015265170512089</v>
+        <v>-0.1976775045286513</v>
       </c>
       <c r="J28" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K28" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L28" t="n">
-        <v>0.01570119478082477</v>
+        <v>0.01519119894497922</v>
       </c>
       <c r="M28" t="n">
-        <v>9.302905659388662</v>
+        <v>9.294652381953936</v>
       </c>
       <c r="N28" t="n">
-        <v>135.5988868469231</v>
+        <v>135.3131213099225</v>
       </c>
       <c r="O28" t="n">
-        <v>11.64469350592462</v>
+        <v>11.63241683013132</v>
       </c>
       <c r="P28" t="n">
-        <v>348.4492444516011</v>
+        <v>348.4067768948879</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -37191,28 +37297,28 @@
         <v>0.2</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1390844253259214</v>
+        <v>0.1188559820840525</v>
       </c>
       <c r="J29" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K29" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L29" t="n">
-        <v>0.003471507953408559</v>
+        <v>0.002523703264684096</v>
       </c>
       <c r="M29" t="n">
-        <v>10.26983743691503</v>
+        <v>10.34938084918266</v>
       </c>
       <c r="N29" t="n">
-        <v>291.3585477016189</v>
+        <v>293.8653107086049</v>
       </c>
       <c r="O29" t="n">
-        <v>17.06922809331514</v>
+        <v>17.14250013004535</v>
       </c>
       <c r="P29" t="n">
-        <v>344.5021000987339</v>
+        <v>344.7268827811891</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -37250,7 +37356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD325"/>
+  <dimension ref="A1:AD326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86505,6 +86611,158 @@
         </is>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:42+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>-38.38454399207778,174.6550255126458</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>-38.38397570246973,174.655594016558</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>-38.38336789915863,174.65605570698688</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-38.3827441875638,174.65647440293264</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-38.38212583493921,174.65690760219135</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>-38.38150494755552,174.65733396342424</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>-38.38087834503895,174.65774488827688</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>-38.38018625109896,174.6579787680252</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>-38.37951405550184,174.65827805129027</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>-38.37885033752431,174.6585942970423</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>-38.378145867055565,174.65873134841513</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>-38.37745605238779,174.65892171858945</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>-38.376767175320545,174.6591162708756</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>-38.376117879903326,174.6594861996279</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>-38.37549604545196,174.65997781006897</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>-38.37473980462742,174.65988687958978</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>-38.37406802290798,174.66017536588762</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>-38.373427458843906,174.66056346728604</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>-38.37277166347147,174.66089110252918</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>-38.37211804392387,174.66122613444642</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>-38.37146734114196,174.6615699342913</t>
+        </is>
+      </c>
+      <c r="W326" t="inlineStr">
+        <is>
+          <t>-38.3707927839204,174.66183056465337</t>
+        </is>
+      </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>-38.37013714799619,174.66215958419923</t>
+        </is>
+      </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>-38.369511856201676,174.66259623920286</t>
+        </is>
+      </c>
+      <c r="Z326" t="inlineStr">
+        <is>
+          <t>-38.3688665980168,174.66296210529973</t>
+        </is>
+      </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>-38.36822298438744,174.66334026516083</t>
+        </is>
+      </c>
+      <c r="AB326" t="inlineStr">
+        <is>
+          <t>-38.367538225609394,174.66356688881643</t>
+        </is>
+      </c>
+      <c r="AC326" t="inlineStr">
+        <is>
+          <t>-38.36696477240242,174.66422789169025</t>
+        </is>
+      </c>
+      <c r="AD326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
